--- a/frontend/test_data/header_detection/Large_Valid_Pivoted_Test.xlsx
+++ b/frontend/test_data/header_detection/Large_Valid_Pivoted_Test.xlsx
@@ -5344,7 +5344,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:O200"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5354,37 +5354,43 @@
         <v>Row Preview</v>
       </c>
       <c r="C1" t="str">
-        <v>Density Bonus</v>
+        <v>Pillar 1: Density (%)</v>
       </c>
       <c r="D1" t="str">
-        <v>Data Boundary Signal</v>
+        <v>Pillar 2: Boundary (%)</v>
       </c>
       <c r="E1" t="str">
-        <v>Consistent String Signal</v>
+        <v>Pillar 3: Consistency (%)</v>
       </c>
       <c r="F1" t="str">
-        <v>Consistent Numeric Signal</v>
+        <v>Pillar 4: Traits (%)</v>
       </c>
       <c r="G1" t="str">
         <v>Pure Data Penalty</v>
       </c>
       <c r="H1" t="str">
-        <v>Numeric Data Penalty</v>
+        <v>Mixed Data Penalty</v>
       </c>
       <c r="I1" t="str">
-        <v>Pivoted Series Bonus</v>
+        <v>Search Booster (Pivoted)</v>
       </c>
       <c r="J1" t="str">
-        <v>100% String Bonus</v>
+        <v>Orphan Header Penalty</v>
       </c>
       <c r="K1" t="str">
-        <v>Unique Values Rule</v>
+        <v>Duplicates Penalty</v>
       </c>
       <c r="L1" t="str">
-        <v>Orphan Header Penalty</v>
+        <v>FILLED CELLS</v>
       </c>
       <c r="M1" t="str">
-        <v>TOTAL SCORE</v>
+        <v>TOTAL RAW SCORE</v>
+      </c>
+      <c r="N1" t="str">
+        <v>NORMALIZED SCORE (%)</v>
+      </c>
+      <c r="O1" t="str">
+        <v>Unsupported Pivoted Penalty</v>
       </c>
     </row>
     <row r="2">
@@ -5395,16 +5401,16 @@
         <v>["SMARTBRIDGE DENSE PIVOTED REPORT"]</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -5413,19 +5419,25 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2">
-        <v>17</v>
+        <v>-32</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>-100</v>
       </c>
     </row>
     <row r="3">
@@ -5436,16 +5448,16 @@
         <v>["Period: Multi-Year Sales Grid"]</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -5454,19 +5466,25 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>17</v>
+        <v>-32</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>-100</v>
       </c>
     </row>
     <row r="4">
@@ -5477,16 +5495,16 @@
         <v>["Source: Warehouse DB"]</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -5495,19 +5513,25 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4">
-        <v>17</v>
+        <v>-32</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>-100</v>
       </c>
     </row>
     <row r="5">
@@ -5518,16 +5542,16 @@
         <v>["Product","Region",2021,2022,2023,2024]</v>
       </c>
       <c r="C5">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="F5">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -5536,19 +5560,25 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J5">
         <v>0</v>
       </c>
       <c r="K5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M5">
-        <v>92</v>
+        <v>-20</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>-100</v>
       </c>
     </row>
     <row r="6">
@@ -5559,37 +5589,43 @@
         <v>["Product-100","East",100,120,140,160]</v>
       </c>
       <c r="C6">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G6">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J6">
         <v>0</v>
       </c>
       <c r="K6">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M6">
-        <v>-43</v>
+        <v>-20</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>-100</v>
       </c>
     </row>
     <row r="7">
@@ -5600,37 +5636,43 @@
         <v>["Product-101","West",102,123,144,165]</v>
       </c>
       <c r="C7">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
       <c r="E7">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G7">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J7">
         <v>0</v>
       </c>
       <c r="K7">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M7">
-        <v>-43</v>
+        <v>-20</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>-100</v>
       </c>
     </row>
     <row r="8">
@@ -5641,37 +5683,43 @@
         <v>["Product-102","East",104,126,148,170]</v>
       </c>
       <c r="C8">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G8">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J8">
         <v>0</v>
       </c>
       <c r="K8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M8">
-        <v>-43</v>
+        <v>-20</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>-100</v>
       </c>
     </row>
     <row r="9">
@@ -5682,37 +5730,43 @@
         <v>["Product-103","West",106,129,152,175]</v>
       </c>
       <c r="C9">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D9">
         <v>0</v>
       </c>
       <c r="E9">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G9">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="H9">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J9">
         <v>0</v>
       </c>
       <c r="K9">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M9">
-        <v>-43</v>
+        <v>-20</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>-100</v>
       </c>
     </row>
     <row r="10">
@@ -5723,37 +5777,43 @@
         <v>["Product-104","East",108,132,156,180]</v>
       </c>
       <c r="C10">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D10">
         <v>0</v>
       </c>
       <c r="E10">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G10">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="H10">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J10">
         <v>0</v>
       </c>
       <c r="K10">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M10">
-        <v>-43</v>
+        <v>-20</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>-100</v>
       </c>
     </row>
     <row r="11">
@@ -5764,37 +5824,43 @@
         <v>["Product-105","West",110,135,160,185]</v>
       </c>
       <c r="C11">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D11">
         <v>0</v>
       </c>
       <c r="E11">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G11">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="H11">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J11">
         <v>0</v>
       </c>
       <c r="K11">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M11">
-        <v>-43</v>
+        <v>-20</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>-100</v>
       </c>
     </row>
     <row r="12">
@@ -5805,37 +5871,43 @@
         <v>["Product-106","East",112,138,164,190]</v>
       </c>
       <c r="C12">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D12">
         <v>0</v>
       </c>
       <c r="E12">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G12">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="H12">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J12">
         <v>0</v>
       </c>
       <c r="K12">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M12">
-        <v>-43</v>
+        <v>-20</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>-100</v>
       </c>
     </row>
     <row r="13">
@@ -5846,37 +5918,43 @@
         <v>["Product-107","West",114,141,168,195]</v>
       </c>
       <c r="C13">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D13">
         <v>0</v>
       </c>
       <c r="E13">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G13">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="H13">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J13">
         <v>0</v>
       </c>
       <c r="K13">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M13">
-        <v>-43</v>
+        <v>-20</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>-100</v>
       </c>
     </row>
     <row r="14">
@@ -5887,37 +5965,43 @@
         <v>["Product-108","East",116,144,172,200]</v>
       </c>
       <c r="C14">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D14">
         <v>0</v>
       </c>
       <c r="E14">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G14">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="H14">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J14">
         <v>0</v>
       </c>
       <c r="K14">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M14">
-        <v>-43</v>
+        <v>-20</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>-100</v>
       </c>
     </row>
     <row r="15">
@@ -5928,37 +6012,43 @@
         <v>["Product-109","West",118,147,176,205]</v>
       </c>
       <c r="C15">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D15">
         <v>0</v>
       </c>
       <c r="E15">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="H15">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J15">
         <v>0</v>
       </c>
       <c r="K15">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M15">
-        <v>-43</v>
+        <v>-20</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>-100</v>
       </c>
     </row>
     <row r="16">
@@ -5969,37 +6059,43 @@
         <v>["Product-110","East",120,150,180,210]</v>
       </c>
       <c r="C16">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D16">
         <v>0</v>
       </c>
       <c r="E16">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G16">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="H16">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J16">
         <v>0</v>
       </c>
       <c r="K16">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M16">
-        <v>-43</v>
+        <v>-20</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>-100</v>
       </c>
     </row>
     <row r="17">
@@ -6010,37 +6106,43 @@
         <v>["Product-111","West",122,153,184,215]</v>
       </c>
       <c r="C17">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D17">
         <v>0</v>
       </c>
       <c r="E17">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G17">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="H17">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J17">
         <v>0</v>
       </c>
       <c r="K17">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M17">
-        <v>-43</v>
+        <v>-20</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>-100</v>
       </c>
     </row>
     <row r="18">
@@ -6051,37 +6153,43 @@
         <v>["Product-112","East",124,156,188,220]</v>
       </c>
       <c r="C18">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D18">
         <v>0</v>
       </c>
       <c r="E18">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G18">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="H18">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J18">
         <v>0</v>
       </c>
       <c r="K18">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M18">
-        <v>-43</v>
+        <v>-20</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>-100</v>
       </c>
     </row>
     <row r="19">
@@ -6092,37 +6200,43 @@
         <v>["Product-113","West",126,159,192,225]</v>
       </c>
       <c r="C19">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D19">
         <v>0</v>
       </c>
       <c r="E19">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G19">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="H19">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J19">
         <v>0</v>
       </c>
       <c r="K19">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M19">
-        <v>-43</v>
+        <v>-20</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>-100</v>
       </c>
     </row>
     <row r="20">
@@ -6133,42 +6247,8508 @@
         <v>["Product-114","East",128,162,196,230]</v>
       </c>
       <c r="C20">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D20">
         <v>0</v>
       </c>
       <c r="E20">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G20">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="H20">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J20">
         <v>0</v>
       </c>
       <c r="K20">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M20">
-        <v>-43</v>
+        <v>-20</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>21</v>
+      </c>
+      <c r="B21" t="str">
+        <v>["Product-115","West",130,165,200,235]</v>
+      </c>
+      <c r="C21">
+        <v>20</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>35</v>
+      </c>
+      <c r="F21">
+        <v>5</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>20</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>6</v>
+      </c>
+      <c r="M21">
+        <v>-20</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>22</v>
+      </c>
+      <c r="B22" t="str">
+        <v>["Product-116","East",132,168,204,240]</v>
+      </c>
+      <c r="C22">
+        <v>20</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>35</v>
+      </c>
+      <c r="F22">
+        <v>5</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>20</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>6</v>
+      </c>
+      <c r="M22">
+        <v>-20</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>23</v>
+      </c>
+      <c r="B23" t="str">
+        <v>["Product-117","West",134,171,208,245]</v>
+      </c>
+      <c r="C23">
+        <v>20</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>35</v>
+      </c>
+      <c r="F23">
+        <v>5</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>20</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>6</v>
+      </c>
+      <c r="M23">
+        <v>-20</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>24</v>
+      </c>
+      <c r="B24" t="str">
+        <v>["Product-118","East",136,174,212,250]</v>
+      </c>
+      <c r="C24">
+        <v>20</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>35</v>
+      </c>
+      <c r="F24">
+        <v>5</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>20</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>6</v>
+      </c>
+      <c r="M24">
+        <v>-20</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>25</v>
+      </c>
+      <c r="B25" t="str">
+        <v>["Product-119","West",138,177,216,255]</v>
+      </c>
+      <c r="C25">
+        <v>20</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>35</v>
+      </c>
+      <c r="F25">
+        <v>5</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>20</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>6</v>
+      </c>
+      <c r="M25">
+        <v>-20</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>26</v>
+      </c>
+      <c r="B26" t="str">
+        <v>["Product-120","East",140,180,220,260]</v>
+      </c>
+      <c r="C26">
+        <v>20</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <v>35</v>
+      </c>
+      <c r="F26">
+        <v>5</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>20</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <v>6</v>
+      </c>
+      <c r="M26">
+        <v>-20</v>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>27</v>
+      </c>
+      <c r="B27" t="str">
+        <v>["Product-121","West",142,183,224,265]</v>
+      </c>
+      <c r="C27">
+        <v>20</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="E27">
+        <v>35</v>
+      </c>
+      <c r="F27">
+        <v>5</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>20</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <v>6</v>
+      </c>
+      <c r="M27">
+        <v>-20</v>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>28</v>
+      </c>
+      <c r="B28" t="str">
+        <v>["Product-122","East",144,186,228,270]</v>
+      </c>
+      <c r="C28">
+        <v>20</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28">
+        <v>35</v>
+      </c>
+      <c r="F28">
+        <v>5</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>20</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <v>6</v>
+      </c>
+      <c r="M28">
+        <v>-20</v>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>29</v>
+      </c>
+      <c r="B29" t="str">
+        <v>["Product-123","West",146,189,232,275]</v>
+      </c>
+      <c r="C29">
+        <v>20</v>
+      </c>
+      <c r="D29">
+        <v>0</v>
+      </c>
+      <c r="E29">
+        <v>35</v>
+      </c>
+      <c r="F29">
+        <v>5</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>20</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <v>6</v>
+      </c>
+      <c r="M29">
+        <v>-20</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>30</v>
+      </c>
+      <c r="B30" t="str">
+        <v>["Product-124","East",148,192,236,280]</v>
+      </c>
+      <c r="C30">
+        <v>20</v>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30">
+        <v>35</v>
+      </c>
+      <c r="F30">
+        <v>5</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>20</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
+      <c r="L30">
+        <v>6</v>
+      </c>
+      <c r="M30">
+        <v>-20</v>
+      </c>
+      <c r="N30">
+        <v>0</v>
+      </c>
+      <c r="O30">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>31</v>
+      </c>
+      <c r="B31" t="str">
+        <v>["Product-125","West",150,195,240,285]</v>
+      </c>
+      <c r="C31">
+        <v>20</v>
+      </c>
+      <c r="D31">
+        <v>0</v>
+      </c>
+      <c r="E31">
+        <v>35</v>
+      </c>
+      <c r="F31">
+        <v>5</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>20</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>0</v>
+      </c>
+      <c r="L31">
+        <v>6</v>
+      </c>
+      <c r="M31">
+        <v>-20</v>
+      </c>
+      <c r="N31">
+        <v>0</v>
+      </c>
+      <c r="O31">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>32</v>
+      </c>
+      <c r="B32" t="str">
+        <v>["Product-126","East",152,198,244,290]</v>
+      </c>
+      <c r="C32">
+        <v>20</v>
+      </c>
+      <c r="D32">
+        <v>0</v>
+      </c>
+      <c r="E32">
+        <v>35</v>
+      </c>
+      <c r="F32">
+        <v>5</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>20</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>0</v>
+      </c>
+      <c r="L32">
+        <v>6</v>
+      </c>
+      <c r="M32">
+        <v>-20</v>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>33</v>
+      </c>
+      <c r="B33" t="str">
+        <v>["Product-127","West",154,201,248,295]</v>
+      </c>
+      <c r="C33">
+        <v>20</v>
+      </c>
+      <c r="D33">
+        <v>0</v>
+      </c>
+      <c r="E33">
+        <v>35</v>
+      </c>
+      <c r="F33">
+        <v>5</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <v>20</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>0</v>
+      </c>
+      <c r="L33">
+        <v>6</v>
+      </c>
+      <c r="M33">
+        <v>-20</v>
+      </c>
+      <c r="N33">
+        <v>0</v>
+      </c>
+      <c r="O33">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>34</v>
+      </c>
+      <c r="B34" t="str">
+        <v>["Product-128","East",156,204,252,300]</v>
+      </c>
+      <c r="C34">
+        <v>20</v>
+      </c>
+      <c r="D34">
+        <v>0</v>
+      </c>
+      <c r="E34">
+        <v>35</v>
+      </c>
+      <c r="F34">
+        <v>5</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34">
+        <v>20</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>0</v>
+      </c>
+      <c r="L34">
+        <v>6</v>
+      </c>
+      <c r="M34">
+        <v>-20</v>
+      </c>
+      <c r="N34">
+        <v>0</v>
+      </c>
+      <c r="O34">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>35</v>
+      </c>
+      <c r="B35" t="str">
+        <v>["Product-129","West",158,207,256,305]</v>
+      </c>
+      <c r="C35">
+        <v>20</v>
+      </c>
+      <c r="D35">
+        <v>0</v>
+      </c>
+      <c r="E35">
+        <v>35</v>
+      </c>
+      <c r="F35">
+        <v>5</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35">
+        <v>20</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>0</v>
+      </c>
+      <c r="L35">
+        <v>6</v>
+      </c>
+      <c r="M35">
+        <v>-20</v>
+      </c>
+      <c r="N35">
+        <v>0</v>
+      </c>
+      <c r="O35">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>36</v>
+      </c>
+      <c r="B36" t="str">
+        <v>["Product-130","East",160,210,260,310]</v>
+      </c>
+      <c r="C36">
+        <v>20</v>
+      </c>
+      <c r="D36">
+        <v>0</v>
+      </c>
+      <c r="E36">
+        <v>35</v>
+      </c>
+      <c r="F36">
+        <v>5</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36">
+        <v>20</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>0</v>
+      </c>
+      <c r="L36">
+        <v>6</v>
+      </c>
+      <c r="M36">
+        <v>-20</v>
+      </c>
+      <c r="N36">
+        <v>0</v>
+      </c>
+      <c r="O36">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>37</v>
+      </c>
+      <c r="B37" t="str">
+        <v>["Product-131","West",162,213,264,315]</v>
+      </c>
+      <c r="C37">
+        <v>20</v>
+      </c>
+      <c r="D37">
+        <v>0</v>
+      </c>
+      <c r="E37">
+        <v>35</v>
+      </c>
+      <c r="F37">
+        <v>5</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="I37">
+        <v>20</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <v>0</v>
+      </c>
+      <c r="L37">
+        <v>6</v>
+      </c>
+      <c r="M37">
+        <v>-20</v>
+      </c>
+      <c r="N37">
+        <v>0</v>
+      </c>
+      <c r="O37">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>38</v>
+      </c>
+      <c r="B38" t="str">
+        <v>["Product-132","East",164,216,268,320]</v>
+      </c>
+      <c r="C38">
+        <v>20</v>
+      </c>
+      <c r="D38">
+        <v>0</v>
+      </c>
+      <c r="E38">
+        <v>35</v>
+      </c>
+      <c r="F38">
+        <v>5</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+      <c r="I38">
+        <v>20</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>0</v>
+      </c>
+      <c r="L38">
+        <v>6</v>
+      </c>
+      <c r="M38">
+        <v>-20</v>
+      </c>
+      <c r="N38">
+        <v>0</v>
+      </c>
+      <c r="O38">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>39</v>
+      </c>
+      <c r="B39" t="str">
+        <v>["Product-133","West",166,219,272,325]</v>
+      </c>
+      <c r="C39">
+        <v>20</v>
+      </c>
+      <c r="D39">
+        <v>0</v>
+      </c>
+      <c r="E39">
+        <v>35</v>
+      </c>
+      <c r="F39">
+        <v>5</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
+      </c>
+      <c r="I39">
+        <v>20</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <v>0</v>
+      </c>
+      <c r="L39">
+        <v>6</v>
+      </c>
+      <c r="M39">
+        <v>-20</v>
+      </c>
+      <c r="N39">
+        <v>0</v>
+      </c>
+      <c r="O39">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>40</v>
+      </c>
+      <c r="B40" t="str">
+        <v>["Product-134","East",168,222,276,330]</v>
+      </c>
+      <c r="C40">
+        <v>20</v>
+      </c>
+      <c r="D40">
+        <v>0</v>
+      </c>
+      <c r="E40">
+        <v>35</v>
+      </c>
+      <c r="F40">
+        <v>5</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+      <c r="I40">
+        <v>20</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>0</v>
+      </c>
+      <c r="L40">
+        <v>6</v>
+      </c>
+      <c r="M40">
+        <v>-20</v>
+      </c>
+      <c r="N40">
+        <v>0</v>
+      </c>
+      <c r="O40">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>41</v>
+      </c>
+      <c r="B41" t="str">
+        <v>["Product-135","West",170,225,280,335]</v>
+      </c>
+      <c r="C41">
+        <v>20</v>
+      </c>
+      <c r="D41">
+        <v>0</v>
+      </c>
+      <c r="E41">
+        <v>35</v>
+      </c>
+      <c r="F41">
+        <v>5</v>
+      </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41">
+        <v>0</v>
+      </c>
+      <c r="I41">
+        <v>20</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41">
+        <v>0</v>
+      </c>
+      <c r="L41">
+        <v>6</v>
+      </c>
+      <c r="M41">
+        <v>-20</v>
+      </c>
+      <c r="N41">
+        <v>0</v>
+      </c>
+      <c r="O41">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>42</v>
+      </c>
+      <c r="B42" t="str">
+        <v>["Product-136","East",172,228,284,340]</v>
+      </c>
+      <c r="C42">
+        <v>20</v>
+      </c>
+      <c r="D42">
+        <v>0</v>
+      </c>
+      <c r="E42">
+        <v>35</v>
+      </c>
+      <c r="F42">
+        <v>5</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+      <c r="I42">
+        <v>20</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42">
+        <v>0</v>
+      </c>
+      <c r="L42">
+        <v>6</v>
+      </c>
+      <c r="M42">
+        <v>-20</v>
+      </c>
+      <c r="N42">
+        <v>0</v>
+      </c>
+      <c r="O42">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>43</v>
+      </c>
+      <c r="B43" t="str">
+        <v>["Product-137","West",174,231,288,345]</v>
+      </c>
+      <c r="C43">
+        <v>20</v>
+      </c>
+      <c r="D43">
+        <v>0</v>
+      </c>
+      <c r="E43">
+        <v>35</v>
+      </c>
+      <c r="F43">
+        <v>5</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+      <c r="I43">
+        <v>20</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <v>0</v>
+      </c>
+      <c r="L43">
+        <v>6</v>
+      </c>
+      <c r="M43">
+        <v>-20</v>
+      </c>
+      <c r="N43">
+        <v>0</v>
+      </c>
+      <c r="O43">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>44</v>
+      </c>
+      <c r="B44" t="str">
+        <v>["Product-138","East",176,234,292,350]</v>
+      </c>
+      <c r="C44">
+        <v>20</v>
+      </c>
+      <c r="D44">
+        <v>0</v>
+      </c>
+      <c r="E44">
+        <v>35</v>
+      </c>
+      <c r="F44">
+        <v>5</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
+      </c>
+      <c r="I44">
+        <v>20</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44">
+        <v>0</v>
+      </c>
+      <c r="L44">
+        <v>6</v>
+      </c>
+      <c r="M44">
+        <v>-20</v>
+      </c>
+      <c r="N44">
+        <v>0</v>
+      </c>
+      <c r="O44">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>45</v>
+      </c>
+      <c r="B45" t="str">
+        <v>["Product-139","West",178,237,296,355]</v>
+      </c>
+      <c r="C45">
+        <v>20</v>
+      </c>
+      <c r="D45">
+        <v>0</v>
+      </c>
+      <c r="E45">
+        <v>35</v>
+      </c>
+      <c r="F45">
+        <v>5</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>0</v>
+      </c>
+      <c r="I45">
+        <v>20</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45">
+        <v>0</v>
+      </c>
+      <c r="L45">
+        <v>6</v>
+      </c>
+      <c r="M45">
+        <v>-20</v>
+      </c>
+      <c r="N45">
+        <v>0</v>
+      </c>
+      <c r="O45">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>46</v>
+      </c>
+      <c r="B46" t="str">
+        <v>["Product-140","East",180,240,300,360]</v>
+      </c>
+      <c r="C46">
+        <v>20</v>
+      </c>
+      <c r="D46">
+        <v>0</v>
+      </c>
+      <c r="E46">
+        <v>35</v>
+      </c>
+      <c r="F46">
+        <v>5</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
+      </c>
+      <c r="I46">
+        <v>20</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46">
+        <v>0</v>
+      </c>
+      <c r="L46">
+        <v>6</v>
+      </c>
+      <c r="M46">
+        <v>-20</v>
+      </c>
+      <c r="N46">
+        <v>0</v>
+      </c>
+      <c r="O46">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>47</v>
+      </c>
+      <c r="B47" t="str">
+        <v>["Product-141","West",182,243,304,365]</v>
+      </c>
+      <c r="C47">
+        <v>20</v>
+      </c>
+      <c r="D47">
+        <v>0</v>
+      </c>
+      <c r="E47">
+        <v>35</v>
+      </c>
+      <c r="F47">
+        <v>5</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>0</v>
+      </c>
+      <c r="I47">
+        <v>20</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47">
+        <v>0</v>
+      </c>
+      <c r="L47">
+        <v>6</v>
+      </c>
+      <c r="M47">
+        <v>-20</v>
+      </c>
+      <c r="N47">
+        <v>0</v>
+      </c>
+      <c r="O47">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>48</v>
+      </c>
+      <c r="B48" t="str">
+        <v>["Product-142","East",184,246,308,370]</v>
+      </c>
+      <c r="C48">
+        <v>20</v>
+      </c>
+      <c r="D48">
+        <v>0</v>
+      </c>
+      <c r="E48">
+        <v>35</v>
+      </c>
+      <c r="F48">
+        <v>5</v>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>0</v>
+      </c>
+      <c r="I48">
+        <v>20</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48">
+        <v>0</v>
+      </c>
+      <c r="L48">
+        <v>6</v>
+      </c>
+      <c r="M48">
+        <v>-20</v>
+      </c>
+      <c r="N48">
+        <v>0</v>
+      </c>
+      <c r="O48">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>49</v>
+      </c>
+      <c r="B49" t="str">
+        <v>["Product-143","West",186,249,312,375]</v>
+      </c>
+      <c r="C49">
+        <v>20</v>
+      </c>
+      <c r="D49">
+        <v>0</v>
+      </c>
+      <c r="E49">
+        <v>35</v>
+      </c>
+      <c r="F49">
+        <v>5</v>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49">
+        <v>20</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49">
+        <v>0</v>
+      </c>
+      <c r="L49">
+        <v>6</v>
+      </c>
+      <c r="M49">
+        <v>-20</v>
+      </c>
+      <c r="N49">
+        <v>0</v>
+      </c>
+      <c r="O49">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>50</v>
+      </c>
+      <c r="B50" t="str">
+        <v>["Product-144","East",188,252,316,380]</v>
+      </c>
+      <c r="C50">
+        <v>20</v>
+      </c>
+      <c r="D50">
+        <v>0</v>
+      </c>
+      <c r="E50">
+        <v>35</v>
+      </c>
+      <c r="F50">
+        <v>5</v>
+      </c>
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <v>0</v>
+      </c>
+      <c r="I50">
+        <v>20</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50">
+        <v>0</v>
+      </c>
+      <c r="L50">
+        <v>6</v>
+      </c>
+      <c r="M50">
+        <v>-20</v>
+      </c>
+      <c r="N50">
+        <v>0</v>
+      </c>
+      <c r="O50">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>51</v>
+      </c>
+      <c r="B51" t="str">
+        <v>["Product-145","West",190,255,320,385]</v>
+      </c>
+      <c r="C51">
+        <v>20</v>
+      </c>
+      <c r="D51">
+        <v>0</v>
+      </c>
+      <c r="E51">
+        <v>35</v>
+      </c>
+      <c r="F51">
+        <v>5</v>
+      </c>
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51">
+        <v>0</v>
+      </c>
+      <c r="I51">
+        <v>20</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
+      <c r="K51">
+        <v>0</v>
+      </c>
+      <c r="L51">
+        <v>6</v>
+      </c>
+      <c r="M51">
+        <v>-20</v>
+      </c>
+      <c r="N51">
+        <v>0</v>
+      </c>
+      <c r="O51">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>52</v>
+      </c>
+      <c r="B52" t="str">
+        <v>["Product-146","East",192,258,324,390]</v>
+      </c>
+      <c r="C52">
+        <v>20</v>
+      </c>
+      <c r="D52">
+        <v>0</v>
+      </c>
+      <c r="E52">
+        <v>35</v>
+      </c>
+      <c r="F52">
+        <v>5</v>
+      </c>
+      <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="H52">
+        <v>0</v>
+      </c>
+      <c r="I52">
+        <v>20</v>
+      </c>
+      <c r="J52">
+        <v>0</v>
+      </c>
+      <c r="K52">
+        <v>0</v>
+      </c>
+      <c r="L52">
+        <v>6</v>
+      </c>
+      <c r="M52">
+        <v>-20</v>
+      </c>
+      <c r="N52">
+        <v>0</v>
+      </c>
+      <c r="O52">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>53</v>
+      </c>
+      <c r="B53" t="str">
+        <v>["Product-147","West",194,261,328,395]</v>
+      </c>
+      <c r="C53">
+        <v>20</v>
+      </c>
+      <c r="D53">
+        <v>0</v>
+      </c>
+      <c r="E53">
+        <v>35</v>
+      </c>
+      <c r="F53">
+        <v>5</v>
+      </c>
+      <c r="G53">
+        <v>0</v>
+      </c>
+      <c r="H53">
+        <v>0</v>
+      </c>
+      <c r="I53">
+        <v>20</v>
+      </c>
+      <c r="J53">
+        <v>0</v>
+      </c>
+      <c r="K53">
+        <v>0</v>
+      </c>
+      <c r="L53">
+        <v>6</v>
+      </c>
+      <c r="M53">
+        <v>-20</v>
+      </c>
+      <c r="N53">
+        <v>0</v>
+      </c>
+      <c r="O53">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>54</v>
+      </c>
+      <c r="B54" t="str">
+        <v>["Product-148","East",196,264,332,400]</v>
+      </c>
+      <c r="C54">
+        <v>20</v>
+      </c>
+      <c r="D54">
+        <v>0</v>
+      </c>
+      <c r="E54">
+        <v>35</v>
+      </c>
+      <c r="F54">
+        <v>5</v>
+      </c>
+      <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54">
+        <v>0</v>
+      </c>
+      <c r="I54">
+        <v>20</v>
+      </c>
+      <c r="J54">
+        <v>0</v>
+      </c>
+      <c r="K54">
+        <v>0</v>
+      </c>
+      <c r="L54">
+        <v>6</v>
+      </c>
+      <c r="M54">
+        <v>-20</v>
+      </c>
+      <c r="N54">
+        <v>0</v>
+      </c>
+      <c r="O54">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>55</v>
+      </c>
+      <c r="B55" t="str">
+        <v>["Product-149","West",198,267,336,405]</v>
+      </c>
+      <c r="C55">
+        <v>20</v>
+      </c>
+      <c r="D55">
+        <v>0</v>
+      </c>
+      <c r="E55">
+        <v>35</v>
+      </c>
+      <c r="F55">
+        <v>5</v>
+      </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+      <c r="I55">
+        <v>20</v>
+      </c>
+      <c r="J55">
+        <v>0</v>
+      </c>
+      <c r="K55">
+        <v>0</v>
+      </c>
+      <c r="L55">
+        <v>6</v>
+      </c>
+      <c r="M55">
+        <v>-20</v>
+      </c>
+      <c r="N55">
+        <v>0</v>
+      </c>
+      <c r="O55">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>56</v>
+      </c>
+      <c r="B56" t="str">
+        <v>["Product-150","East",200,270,340,410]</v>
+      </c>
+      <c r="C56">
+        <v>20</v>
+      </c>
+      <c r="D56">
+        <v>0</v>
+      </c>
+      <c r="E56">
+        <v>35</v>
+      </c>
+      <c r="F56">
+        <v>5</v>
+      </c>
+      <c r="G56">
+        <v>0</v>
+      </c>
+      <c r="H56">
+        <v>0</v>
+      </c>
+      <c r="I56">
+        <v>20</v>
+      </c>
+      <c r="J56">
+        <v>0</v>
+      </c>
+      <c r="K56">
+        <v>0</v>
+      </c>
+      <c r="L56">
+        <v>6</v>
+      </c>
+      <c r="M56">
+        <v>-20</v>
+      </c>
+      <c r="N56">
+        <v>0</v>
+      </c>
+      <c r="O56">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>57</v>
+      </c>
+      <c r="B57" t="str">
+        <v>["Product-151","West",202,273,344,415]</v>
+      </c>
+      <c r="C57">
+        <v>20</v>
+      </c>
+      <c r="D57">
+        <v>0</v>
+      </c>
+      <c r="E57">
+        <v>35</v>
+      </c>
+      <c r="F57">
+        <v>5</v>
+      </c>
+      <c r="G57">
+        <v>0</v>
+      </c>
+      <c r="H57">
+        <v>0</v>
+      </c>
+      <c r="I57">
+        <v>20</v>
+      </c>
+      <c r="J57">
+        <v>0</v>
+      </c>
+      <c r="K57">
+        <v>0</v>
+      </c>
+      <c r="L57">
+        <v>6</v>
+      </c>
+      <c r="M57">
+        <v>-20</v>
+      </c>
+      <c r="N57">
+        <v>0</v>
+      </c>
+      <c r="O57">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>58</v>
+      </c>
+      <c r="B58" t="str">
+        <v>["Product-152","East",204,276,348,420]</v>
+      </c>
+      <c r="C58">
+        <v>20</v>
+      </c>
+      <c r="D58">
+        <v>0</v>
+      </c>
+      <c r="E58">
+        <v>35</v>
+      </c>
+      <c r="F58">
+        <v>5</v>
+      </c>
+      <c r="G58">
+        <v>0</v>
+      </c>
+      <c r="H58">
+        <v>0</v>
+      </c>
+      <c r="I58">
+        <v>20</v>
+      </c>
+      <c r="J58">
+        <v>0</v>
+      </c>
+      <c r="K58">
+        <v>0</v>
+      </c>
+      <c r="L58">
+        <v>6</v>
+      </c>
+      <c r="M58">
+        <v>-20</v>
+      </c>
+      <c r="N58">
+        <v>0</v>
+      </c>
+      <c r="O58">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>59</v>
+      </c>
+      <c r="B59" t="str">
+        <v>["Product-153","West",206,279,352,425]</v>
+      </c>
+      <c r="C59">
+        <v>20</v>
+      </c>
+      <c r="D59">
+        <v>0</v>
+      </c>
+      <c r="E59">
+        <v>35</v>
+      </c>
+      <c r="F59">
+        <v>5</v>
+      </c>
+      <c r="G59">
+        <v>0</v>
+      </c>
+      <c r="H59">
+        <v>0</v>
+      </c>
+      <c r="I59">
+        <v>20</v>
+      </c>
+      <c r="J59">
+        <v>0</v>
+      </c>
+      <c r="K59">
+        <v>0</v>
+      </c>
+      <c r="L59">
+        <v>6</v>
+      </c>
+      <c r="M59">
+        <v>-20</v>
+      </c>
+      <c r="N59">
+        <v>0</v>
+      </c>
+      <c r="O59">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>60</v>
+      </c>
+      <c r="B60" t="str">
+        <v>["Product-154","East",208,282,356,430]</v>
+      </c>
+      <c r="C60">
+        <v>20</v>
+      </c>
+      <c r="D60">
+        <v>0</v>
+      </c>
+      <c r="E60">
+        <v>35</v>
+      </c>
+      <c r="F60">
+        <v>5</v>
+      </c>
+      <c r="G60">
+        <v>0</v>
+      </c>
+      <c r="H60">
+        <v>0</v>
+      </c>
+      <c r="I60">
+        <v>20</v>
+      </c>
+      <c r="J60">
+        <v>0</v>
+      </c>
+      <c r="K60">
+        <v>0</v>
+      </c>
+      <c r="L60">
+        <v>6</v>
+      </c>
+      <c r="M60">
+        <v>-20</v>
+      </c>
+      <c r="N60">
+        <v>0</v>
+      </c>
+      <c r="O60">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>61</v>
+      </c>
+      <c r="B61" t="str">
+        <v>["Product-155","West",210,285,360,435]</v>
+      </c>
+      <c r="C61">
+        <v>20</v>
+      </c>
+      <c r="D61">
+        <v>0</v>
+      </c>
+      <c r="E61">
+        <v>35</v>
+      </c>
+      <c r="F61">
+        <v>5</v>
+      </c>
+      <c r="G61">
+        <v>0</v>
+      </c>
+      <c r="H61">
+        <v>0</v>
+      </c>
+      <c r="I61">
+        <v>20</v>
+      </c>
+      <c r="J61">
+        <v>0</v>
+      </c>
+      <c r="K61">
+        <v>0</v>
+      </c>
+      <c r="L61">
+        <v>6</v>
+      </c>
+      <c r="M61">
+        <v>-20</v>
+      </c>
+      <c r="N61">
+        <v>0</v>
+      </c>
+      <c r="O61">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>62</v>
+      </c>
+      <c r="B62" t="str">
+        <v>["Product-156","East",212,288,364,440]</v>
+      </c>
+      <c r="C62">
+        <v>20</v>
+      </c>
+      <c r="D62">
+        <v>0</v>
+      </c>
+      <c r="E62">
+        <v>35</v>
+      </c>
+      <c r="F62">
+        <v>5</v>
+      </c>
+      <c r="G62">
+        <v>0</v>
+      </c>
+      <c r="H62">
+        <v>0</v>
+      </c>
+      <c r="I62">
+        <v>20</v>
+      </c>
+      <c r="J62">
+        <v>0</v>
+      </c>
+      <c r="K62">
+        <v>0</v>
+      </c>
+      <c r="L62">
+        <v>6</v>
+      </c>
+      <c r="M62">
+        <v>-20</v>
+      </c>
+      <c r="N62">
+        <v>0</v>
+      </c>
+      <c r="O62">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>63</v>
+      </c>
+      <c r="B63" t="str">
+        <v>["Product-157","West",214,291,368,445]</v>
+      </c>
+      <c r="C63">
+        <v>20</v>
+      </c>
+      <c r="D63">
+        <v>0</v>
+      </c>
+      <c r="E63">
+        <v>35</v>
+      </c>
+      <c r="F63">
+        <v>5</v>
+      </c>
+      <c r="G63">
+        <v>0</v>
+      </c>
+      <c r="H63">
+        <v>0</v>
+      </c>
+      <c r="I63">
+        <v>20</v>
+      </c>
+      <c r="J63">
+        <v>0</v>
+      </c>
+      <c r="K63">
+        <v>0</v>
+      </c>
+      <c r="L63">
+        <v>6</v>
+      </c>
+      <c r="M63">
+        <v>-20</v>
+      </c>
+      <c r="N63">
+        <v>0</v>
+      </c>
+      <c r="O63">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>64</v>
+      </c>
+      <c r="B64" t="str">
+        <v>["Product-158","East",216,294,372,450]</v>
+      </c>
+      <c r="C64">
+        <v>20</v>
+      </c>
+      <c r="D64">
+        <v>0</v>
+      </c>
+      <c r="E64">
+        <v>35</v>
+      </c>
+      <c r="F64">
+        <v>5</v>
+      </c>
+      <c r="G64">
+        <v>0</v>
+      </c>
+      <c r="H64">
+        <v>0</v>
+      </c>
+      <c r="I64">
+        <v>20</v>
+      </c>
+      <c r="J64">
+        <v>0</v>
+      </c>
+      <c r="K64">
+        <v>0</v>
+      </c>
+      <c r="L64">
+        <v>6</v>
+      </c>
+      <c r="M64">
+        <v>-20</v>
+      </c>
+      <c r="N64">
+        <v>0</v>
+      </c>
+      <c r="O64">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>65</v>
+      </c>
+      <c r="B65" t="str">
+        <v>["Product-159","West",218,297,376,455]</v>
+      </c>
+      <c r="C65">
+        <v>20</v>
+      </c>
+      <c r="D65">
+        <v>0</v>
+      </c>
+      <c r="E65">
+        <v>35</v>
+      </c>
+      <c r="F65">
+        <v>5</v>
+      </c>
+      <c r="G65">
+        <v>0</v>
+      </c>
+      <c r="H65">
+        <v>0</v>
+      </c>
+      <c r="I65">
+        <v>20</v>
+      </c>
+      <c r="J65">
+        <v>0</v>
+      </c>
+      <c r="K65">
+        <v>0</v>
+      </c>
+      <c r="L65">
+        <v>6</v>
+      </c>
+      <c r="M65">
+        <v>-20</v>
+      </c>
+      <c r="N65">
+        <v>0</v>
+      </c>
+      <c r="O65">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>66</v>
+      </c>
+      <c r="B66" t="str">
+        <v>["Product-160","East",220,300,380,460]</v>
+      </c>
+      <c r="C66">
+        <v>20</v>
+      </c>
+      <c r="D66">
+        <v>0</v>
+      </c>
+      <c r="E66">
+        <v>35</v>
+      </c>
+      <c r="F66">
+        <v>5</v>
+      </c>
+      <c r="G66">
+        <v>0</v>
+      </c>
+      <c r="H66">
+        <v>0</v>
+      </c>
+      <c r="I66">
+        <v>20</v>
+      </c>
+      <c r="J66">
+        <v>0</v>
+      </c>
+      <c r="K66">
+        <v>0</v>
+      </c>
+      <c r="L66">
+        <v>6</v>
+      </c>
+      <c r="M66">
+        <v>-20</v>
+      </c>
+      <c r="N66">
+        <v>0</v>
+      </c>
+      <c r="O66">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>67</v>
+      </c>
+      <c r="B67" t="str">
+        <v>["Product-161","West",222,303,384,465]</v>
+      </c>
+      <c r="C67">
+        <v>20</v>
+      </c>
+      <c r="D67">
+        <v>0</v>
+      </c>
+      <c r="E67">
+        <v>35</v>
+      </c>
+      <c r="F67">
+        <v>5</v>
+      </c>
+      <c r="G67">
+        <v>0</v>
+      </c>
+      <c r="H67">
+        <v>0</v>
+      </c>
+      <c r="I67">
+        <v>20</v>
+      </c>
+      <c r="J67">
+        <v>0</v>
+      </c>
+      <c r="K67">
+        <v>0</v>
+      </c>
+      <c r="L67">
+        <v>6</v>
+      </c>
+      <c r="M67">
+        <v>-20</v>
+      </c>
+      <c r="N67">
+        <v>0</v>
+      </c>
+      <c r="O67">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>68</v>
+      </c>
+      <c r="B68" t="str">
+        <v>["Product-162","East",224,306,388,470]</v>
+      </c>
+      <c r="C68">
+        <v>20</v>
+      </c>
+      <c r="D68">
+        <v>0</v>
+      </c>
+      <c r="E68">
+        <v>35</v>
+      </c>
+      <c r="F68">
+        <v>5</v>
+      </c>
+      <c r="G68">
+        <v>0</v>
+      </c>
+      <c r="H68">
+        <v>0</v>
+      </c>
+      <c r="I68">
+        <v>20</v>
+      </c>
+      <c r="J68">
+        <v>0</v>
+      </c>
+      <c r="K68">
+        <v>0</v>
+      </c>
+      <c r="L68">
+        <v>6</v>
+      </c>
+      <c r="M68">
+        <v>-20</v>
+      </c>
+      <c r="N68">
+        <v>0</v>
+      </c>
+      <c r="O68">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>69</v>
+      </c>
+      <c r="B69" t="str">
+        <v>["Product-163","West",226,309,392,475]</v>
+      </c>
+      <c r="C69">
+        <v>20</v>
+      </c>
+      <c r="D69">
+        <v>0</v>
+      </c>
+      <c r="E69">
+        <v>35</v>
+      </c>
+      <c r="F69">
+        <v>5</v>
+      </c>
+      <c r="G69">
+        <v>0</v>
+      </c>
+      <c r="H69">
+        <v>0</v>
+      </c>
+      <c r="I69">
+        <v>20</v>
+      </c>
+      <c r="J69">
+        <v>0</v>
+      </c>
+      <c r="K69">
+        <v>0</v>
+      </c>
+      <c r="L69">
+        <v>6</v>
+      </c>
+      <c r="M69">
+        <v>-20</v>
+      </c>
+      <c r="N69">
+        <v>0</v>
+      </c>
+      <c r="O69">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>70</v>
+      </c>
+      <c r="B70" t="str">
+        <v>["Product-164","East",228,312,396,480]</v>
+      </c>
+      <c r="C70">
+        <v>20</v>
+      </c>
+      <c r="D70">
+        <v>0</v>
+      </c>
+      <c r="E70">
+        <v>35</v>
+      </c>
+      <c r="F70">
+        <v>5</v>
+      </c>
+      <c r="G70">
+        <v>0</v>
+      </c>
+      <c r="H70">
+        <v>0</v>
+      </c>
+      <c r="I70">
+        <v>20</v>
+      </c>
+      <c r="J70">
+        <v>0</v>
+      </c>
+      <c r="K70">
+        <v>0</v>
+      </c>
+      <c r="L70">
+        <v>6</v>
+      </c>
+      <c r="M70">
+        <v>-20</v>
+      </c>
+      <c r="N70">
+        <v>0</v>
+      </c>
+      <c r="O70">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>71</v>
+      </c>
+      <c r="B71" t="str">
+        <v>["Product-165","West",230,315,400,485]</v>
+      </c>
+      <c r="C71">
+        <v>20</v>
+      </c>
+      <c r="D71">
+        <v>0</v>
+      </c>
+      <c r="E71">
+        <v>35</v>
+      </c>
+      <c r="F71">
+        <v>5</v>
+      </c>
+      <c r="G71">
+        <v>0</v>
+      </c>
+      <c r="H71">
+        <v>0</v>
+      </c>
+      <c r="I71">
+        <v>20</v>
+      </c>
+      <c r="J71">
+        <v>0</v>
+      </c>
+      <c r="K71">
+        <v>0</v>
+      </c>
+      <c r="L71">
+        <v>6</v>
+      </c>
+      <c r="M71">
+        <v>-20</v>
+      </c>
+      <c r="N71">
+        <v>0</v>
+      </c>
+      <c r="O71">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>72</v>
+      </c>
+      <c r="B72" t="str">
+        <v>["Product-166","East",232,318,404,490]</v>
+      </c>
+      <c r="C72">
+        <v>20</v>
+      </c>
+      <c r="D72">
+        <v>0</v>
+      </c>
+      <c r="E72">
+        <v>35</v>
+      </c>
+      <c r="F72">
+        <v>5</v>
+      </c>
+      <c r="G72">
+        <v>0</v>
+      </c>
+      <c r="H72">
+        <v>0</v>
+      </c>
+      <c r="I72">
+        <v>20</v>
+      </c>
+      <c r="J72">
+        <v>0</v>
+      </c>
+      <c r="K72">
+        <v>0</v>
+      </c>
+      <c r="L72">
+        <v>6</v>
+      </c>
+      <c r="M72">
+        <v>-20</v>
+      </c>
+      <c r="N72">
+        <v>0</v>
+      </c>
+      <c r="O72">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>73</v>
+      </c>
+      <c r="B73" t="str">
+        <v>["Product-167","West",234,321,408,495]</v>
+      </c>
+      <c r="C73">
+        <v>20</v>
+      </c>
+      <c r="D73">
+        <v>0</v>
+      </c>
+      <c r="E73">
+        <v>35</v>
+      </c>
+      <c r="F73">
+        <v>5</v>
+      </c>
+      <c r="G73">
+        <v>0</v>
+      </c>
+      <c r="H73">
+        <v>0</v>
+      </c>
+      <c r="I73">
+        <v>20</v>
+      </c>
+      <c r="J73">
+        <v>0</v>
+      </c>
+      <c r="K73">
+        <v>0</v>
+      </c>
+      <c r="L73">
+        <v>6</v>
+      </c>
+      <c r="M73">
+        <v>-20</v>
+      </c>
+      <c r="N73">
+        <v>0</v>
+      </c>
+      <c r="O73">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>74</v>
+      </c>
+      <c r="B74" t="str">
+        <v>["Product-168","East",236,324,412,500]</v>
+      </c>
+      <c r="C74">
+        <v>20</v>
+      </c>
+      <c r="D74">
+        <v>0</v>
+      </c>
+      <c r="E74">
+        <v>35</v>
+      </c>
+      <c r="F74">
+        <v>5</v>
+      </c>
+      <c r="G74">
+        <v>0</v>
+      </c>
+      <c r="H74">
+        <v>0</v>
+      </c>
+      <c r="I74">
+        <v>20</v>
+      </c>
+      <c r="J74">
+        <v>0</v>
+      </c>
+      <c r="K74">
+        <v>0</v>
+      </c>
+      <c r="L74">
+        <v>6</v>
+      </c>
+      <c r="M74">
+        <v>-20</v>
+      </c>
+      <c r="N74">
+        <v>0</v>
+      </c>
+      <c r="O74">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>75</v>
+      </c>
+      <c r="B75" t="str">
+        <v>["Product-169","West",238,327,416,505]</v>
+      </c>
+      <c r="C75">
+        <v>20</v>
+      </c>
+      <c r="D75">
+        <v>0</v>
+      </c>
+      <c r="E75">
+        <v>35</v>
+      </c>
+      <c r="F75">
+        <v>5</v>
+      </c>
+      <c r="G75">
+        <v>0</v>
+      </c>
+      <c r="H75">
+        <v>0</v>
+      </c>
+      <c r="I75">
+        <v>20</v>
+      </c>
+      <c r="J75">
+        <v>0</v>
+      </c>
+      <c r="K75">
+        <v>0</v>
+      </c>
+      <c r="L75">
+        <v>6</v>
+      </c>
+      <c r="M75">
+        <v>-20</v>
+      </c>
+      <c r="N75">
+        <v>0</v>
+      </c>
+      <c r="O75">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>76</v>
+      </c>
+      <c r="B76" t="str">
+        <v>["Product-170","East",240,330,420,510]</v>
+      </c>
+      <c r="C76">
+        <v>20</v>
+      </c>
+      <c r="D76">
+        <v>0</v>
+      </c>
+      <c r="E76">
+        <v>35</v>
+      </c>
+      <c r="F76">
+        <v>5</v>
+      </c>
+      <c r="G76">
+        <v>0</v>
+      </c>
+      <c r="H76">
+        <v>0</v>
+      </c>
+      <c r="I76">
+        <v>20</v>
+      </c>
+      <c r="J76">
+        <v>0</v>
+      </c>
+      <c r="K76">
+        <v>0</v>
+      </c>
+      <c r="L76">
+        <v>6</v>
+      </c>
+      <c r="M76">
+        <v>-20</v>
+      </c>
+      <c r="N76">
+        <v>0</v>
+      </c>
+      <c r="O76">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>77</v>
+      </c>
+      <c r="B77" t="str">
+        <v>["Product-171","West",242,333,424,515]</v>
+      </c>
+      <c r="C77">
+        <v>20</v>
+      </c>
+      <c r="D77">
+        <v>0</v>
+      </c>
+      <c r="E77">
+        <v>35</v>
+      </c>
+      <c r="F77">
+        <v>5</v>
+      </c>
+      <c r="G77">
+        <v>0</v>
+      </c>
+      <c r="H77">
+        <v>0</v>
+      </c>
+      <c r="I77">
+        <v>20</v>
+      </c>
+      <c r="J77">
+        <v>0</v>
+      </c>
+      <c r="K77">
+        <v>0</v>
+      </c>
+      <c r="L77">
+        <v>6</v>
+      </c>
+      <c r="M77">
+        <v>-20</v>
+      </c>
+      <c r="N77">
+        <v>0</v>
+      </c>
+      <c r="O77">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>78</v>
+      </c>
+      <c r="B78" t="str">
+        <v>["Product-172","East",244,336,428,520]</v>
+      </c>
+      <c r="C78">
+        <v>20</v>
+      </c>
+      <c r="D78">
+        <v>0</v>
+      </c>
+      <c r="E78">
+        <v>35</v>
+      </c>
+      <c r="F78">
+        <v>5</v>
+      </c>
+      <c r="G78">
+        <v>0</v>
+      </c>
+      <c r="H78">
+        <v>0</v>
+      </c>
+      <c r="I78">
+        <v>20</v>
+      </c>
+      <c r="J78">
+        <v>0</v>
+      </c>
+      <c r="K78">
+        <v>0</v>
+      </c>
+      <c r="L78">
+        <v>6</v>
+      </c>
+      <c r="M78">
+        <v>-20</v>
+      </c>
+      <c r="N78">
+        <v>0</v>
+      </c>
+      <c r="O78">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>79</v>
+      </c>
+      <c r="B79" t="str">
+        <v>["Product-173","West",246,339,432,525]</v>
+      </c>
+      <c r="C79">
+        <v>20</v>
+      </c>
+      <c r="D79">
+        <v>0</v>
+      </c>
+      <c r="E79">
+        <v>35</v>
+      </c>
+      <c r="F79">
+        <v>5</v>
+      </c>
+      <c r="G79">
+        <v>0</v>
+      </c>
+      <c r="H79">
+        <v>0</v>
+      </c>
+      <c r="I79">
+        <v>20</v>
+      </c>
+      <c r="J79">
+        <v>0</v>
+      </c>
+      <c r="K79">
+        <v>0</v>
+      </c>
+      <c r="L79">
+        <v>6</v>
+      </c>
+      <c r="M79">
+        <v>-20</v>
+      </c>
+      <c r="N79">
+        <v>0</v>
+      </c>
+      <c r="O79">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>80</v>
+      </c>
+      <c r="B80" t="str">
+        <v>["Product-174","East",248,342,436,530]</v>
+      </c>
+      <c r="C80">
+        <v>20</v>
+      </c>
+      <c r="D80">
+        <v>0</v>
+      </c>
+      <c r="E80">
+        <v>35</v>
+      </c>
+      <c r="F80">
+        <v>5</v>
+      </c>
+      <c r="G80">
+        <v>0</v>
+      </c>
+      <c r="H80">
+        <v>0</v>
+      </c>
+      <c r="I80">
+        <v>20</v>
+      </c>
+      <c r="J80">
+        <v>0</v>
+      </c>
+      <c r="K80">
+        <v>0</v>
+      </c>
+      <c r="L80">
+        <v>6</v>
+      </c>
+      <c r="M80">
+        <v>-20</v>
+      </c>
+      <c r="N80">
+        <v>0</v>
+      </c>
+      <c r="O80">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>81</v>
+      </c>
+      <c r="B81" t="str">
+        <v>["Product-175","West",250,345,440,535]</v>
+      </c>
+      <c r="C81">
+        <v>20</v>
+      </c>
+      <c r="D81">
+        <v>0</v>
+      </c>
+      <c r="E81">
+        <v>35</v>
+      </c>
+      <c r="F81">
+        <v>5</v>
+      </c>
+      <c r="G81">
+        <v>0</v>
+      </c>
+      <c r="H81">
+        <v>0</v>
+      </c>
+      <c r="I81">
+        <v>20</v>
+      </c>
+      <c r="J81">
+        <v>0</v>
+      </c>
+      <c r="K81">
+        <v>0</v>
+      </c>
+      <c r="L81">
+        <v>6</v>
+      </c>
+      <c r="M81">
+        <v>-20</v>
+      </c>
+      <c r="N81">
+        <v>0</v>
+      </c>
+      <c r="O81">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>82</v>
+      </c>
+      <c r="B82" t="str">
+        <v>["Product-176","East",252,348,444,540]</v>
+      </c>
+      <c r="C82">
+        <v>20</v>
+      </c>
+      <c r="D82">
+        <v>0</v>
+      </c>
+      <c r="E82">
+        <v>35</v>
+      </c>
+      <c r="F82">
+        <v>5</v>
+      </c>
+      <c r="G82">
+        <v>0</v>
+      </c>
+      <c r="H82">
+        <v>0</v>
+      </c>
+      <c r="I82">
+        <v>20</v>
+      </c>
+      <c r="J82">
+        <v>0</v>
+      </c>
+      <c r="K82">
+        <v>0</v>
+      </c>
+      <c r="L82">
+        <v>6</v>
+      </c>
+      <c r="M82">
+        <v>-20</v>
+      </c>
+      <c r="N82">
+        <v>0</v>
+      </c>
+      <c r="O82">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>83</v>
+      </c>
+      <c r="B83" t="str">
+        <v>["Product-177","West",254,351,448,545]</v>
+      </c>
+      <c r="C83">
+        <v>20</v>
+      </c>
+      <c r="D83">
+        <v>0</v>
+      </c>
+      <c r="E83">
+        <v>35</v>
+      </c>
+      <c r="F83">
+        <v>5</v>
+      </c>
+      <c r="G83">
+        <v>0</v>
+      </c>
+      <c r="H83">
+        <v>0</v>
+      </c>
+      <c r="I83">
+        <v>20</v>
+      </c>
+      <c r="J83">
+        <v>0</v>
+      </c>
+      <c r="K83">
+        <v>0</v>
+      </c>
+      <c r="L83">
+        <v>6</v>
+      </c>
+      <c r="M83">
+        <v>-20</v>
+      </c>
+      <c r="N83">
+        <v>0</v>
+      </c>
+      <c r="O83">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>84</v>
+      </c>
+      <c r="B84" t="str">
+        <v>["Product-178","East",256,354,452,550]</v>
+      </c>
+      <c r="C84">
+        <v>20</v>
+      </c>
+      <c r="D84">
+        <v>0</v>
+      </c>
+      <c r="E84">
+        <v>35</v>
+      </c>
+      <c r="F84">
+        <v>5</v>
+      </c>
+      <c r="G84">
+        <v>0</v>
+      </c>
+      <c r="H84">
+        <v>0</v>
+      </c>
+      <c r="I84">
+        <v>20</v>
+      </c>
+      <c r="J84">
+        <v>0</v>
+      </c>
+      <c r="K84">
+        <v>0</v>
+      </c>
+      <c r="L84">
+        <v>6</v>
+      </c>
+      <c r="M84">
+        <v>-20</v>
+      </c>
+      <c r="N84">
+        <v>0</v>
+      </c>
+      <c r="O84">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>85</v>
+      </c>
+      <c r="B85" t="str">
+        <v>["Product-179","West",258,357,456,555]</v>
+      </c>
+      <c r="C85">
+        <v>20</v>
+      </c>
+      <c r="D85">
+        <v>0</v>
+      </c>
+      <c r="E85">
+        <v>35</v>
+      </c>
+      <c r="F85">
+        <v>5</v>
+      </c>
+      <c r="G85">
+        <v>0</v>
+      </c>
+      <c r="H85">
+        <v>0</v>
+      </c>
+      <c r="I85">
+        <v>20</v>
+      </c>
+      <c r="J85">
+        <v>0</v>
+      </c>
+      <c r="K85">
+        <v>0</v>
+      </c>
+      <c r="L85">
+        <v>6</v>
+      </c>
+      <c r="M85">
+        <v>-20</v>
+      </c>
+      <c r="N85">
+        <v>0</v>
+      </c>
+      <c r="O85">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>86</v>
+      </c>
+      <c r="B86" t="str">
+        <v>["Product-180","East",260,360,460,560]</v>
+      </c>
+      <c r="C86">
+        <v>20</v>
+      </c>
+      <c r="D86">
+        <v>0</v>
+      </c>
+      <c r="E86">
+        <v>35</v>
+      </c>
+      <c r="F86">
+        <v>5</v>
+      </c>
+      <c r="G86">
+        <v>0</v>
+      </c>
+      <c r="H86">
+        <v>0</v>
+      </c>
+      <c r="I86">
+        <v>20</v>
+      </c>
+      <c r="J86">
+        <v>0</v>
+      </c>
+      <c r="K86">
+        <v>0</v>
+      </c>
+      <c r="L86">
+        <v>6</v>
+      </c>
+      <c r="M86">
+        <v>-20</v>
+      </c>
+      <c r="N86">
+        <v>0</v>
+      </c>
+      <c r="O86">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>87</v>
+      </c>
+      <c r="B87" t="str">
+        <v>["Product-181","West",262,363,464,565]</v>
+      </c>
+      <c r="C87">
+        <v>20</v>
+      </c>
+      <c r="D87">
+        <v>0</v>
+      </c>
+      <c r="E87">
+        <v>35</v>
+      </c>
+      <c r="F87">
+        <v>5</v>
+      </c>
+      <c r="G87">
+        <v>0</v>
+      </c>
+      <c r="H87">
+        <v>0</v>
+      </c>
+      <c r="I87">
+        <v>20</v>
+      </c>
+      <c r="J87">
+        <v>0</v>
+      </c>
+      <c r="K87">
+        <v>0</v>
+      </c>
+      <c r="L87">
+        <v>6</v>
+      </c>
+      <c r="M87">
+        <v>-20</v>
+      </c>
+      <c r="N87">
+        <v>0</v>
+      </c>
+      <c r="O87">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>88</v>
+      </c>
+      <c r="B88" t="str">
+        <v>["Product-182","East",264,366,468,570]</v>
+      </c>
+      <c r="C88">
+        <v>20</v>
+      </c>
+      <c r="D88">
+        <v>0</v>
+      </c>
+      <c r="E88">
+        <v>35</v>
+      </c>
+      <c r="F88">
+        <v>5</v>
+      </c>
+      <c r="G88">
+        <v>0</v>
+      </c>
+      <c r="H88">
+        <v>0</v>
+      </c>
+      <c r="I88">
+        <v>20</v>
+      </c>
+      <c r="J88">
+        <v>0</v>
+      </c>
+      <c r="K88">
+        <v>0</v>
+      </c>
+      <c r="L88">
+        <v>6</v>
+      </c>
+      <c r="M88">
+        <v>-20</v>
+      </c>
+      <c r="N88">
+        <v>0</v>
+      </c>
+      <c r="O88">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>89</v>
+      </c>
+      <c r="B89" t="str">
+        <v>["Product-183","West",266,369,472,575]</v>
+      </c>
+      <c r="C89">
+        <v>20</v>
+      </c>
+      <c r="D89">
+        <v>0</v>
+      </c>
+      <c r="E89">
+        <v>35</v>
+      </c>
+      <c r="F89">
+        <v>5</v>
+      </c>
+      <c r="G89">
+        <v>0</v>
+      </c>
+      <c r="H89">
+        <v>0</v>
+      </c>
+      <c r="I89">
+        <v>20</v>
+      </c>
+      <c r="J89">
+        <v>0</v>
+      </c>
+      <c r="K89">
+        <v>0</v>
+      </c>
+      <c r="L89">
+        <v>6</v>
+      </c>
+      <c r="M89">
+        <v>-20</v>
+      </c>
+      <c r="N89">
+        <v>0</v>
+      </c>
+      <c r="O89">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>90</v>
+      </c>
+      <c r="B90" t="str">
+        <v>["Product-184","East",268,372,476,580]</v>
+      </c>
+      <c r="C90">
+        <v>20</v>
+      </c>
+      <c r="D90">
+        <v>0</v>
+      </c>
+      <c r="E90">
+        <v>35</v>
+      </c>
+      <c r="F90">
+        <v>5</v>
+      </c>
+      <c r="G90">
+        <v>0</v>
+      </c>
+      <c r="H90">
+        <v>0</v>
+      </c>
+      <c r="I90">
+        <v>20</v>
+      </c>
+      <c r="J90">
+        <v>0</v>
+      </c>
+      <c r="K90">
+        <v>0</v>
+      </c>
+      <c r="L90">
+        <v>6</v>
+      </c>
+      <c r="M90">
+        <v>-20</v>
+      </c>
+      <c r="N90">
+        <v>0</v>
+      </c>
+      <c r="O90">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>91</v>
+      </c>
+      <c r="B91" t="str">
+        <v>["Product-185","West",270,375,480,585]</v>
+      </c>
+      <c r="C91">
+        <v>20</v>
+      </c>
+      <c r="D91">
+        <v>0</v>
+      </c>
+      <c r="E91">
+        <v>35</v>
+      </c>
+      <c r="F91">
+        <v>5</v>
+      </c>
+      <c r="G91">
+        <v>0</v>
+      </c>
+      <c r="H91">
+        <v>0</v>
+      </c>
+      <c r="I91">
+        <v>20</v>
+      </c>
+      <c r="J91">
+        <v>0</v>
+      </c>
+      <c r="K91">
+        <v>0</v>
+      </c>
+      <c r="L91">
+        <v>6</v>
+      </c>
+      <c r="M91">
+        <v>-20</v>
+      </c>
+      <c r="N91">
+        <v>0</v>
+      </c>
+      <c r="O91">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>92</v>
+      </c>
+      <c r="B92" t="str">
+        <v>["Product-186","East",272,378,484,590]</v>
+      </c>
+      <c r="C92">
+        <v>20</v>
+      </c>
+      <c r="D92">
+        <v>0</v>
+      </c>
+      <c r="E92">
+        <v>35</v>
+      </c>
+      <c r="F92">
+        <v>5</v>
+      </c>
+      <c r="G92">
+        <v>0</v>
+      </c>
+      <c r="H92">
+        <v>0</v>
+      </c>
+      <c r="I92">
+        <v>20</v>
+      </c>
+      <c r="J92">
+        <v>0</v>
+      </c>
+      <c r="K92">
+        <v>0</v>
+      </c>
+      <c r="L92">
+        <v>6</v>
+      </c>
+      <c r="M92">
+        <v>-20</v>
+      </c>
+      <c r="N92">
+        <v>0</v>
+      </c>
+      <c r="O92">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>93</v>
+      </c>
+      <c r="B93" t="str">
+        <v>["Product-187","West",274,381,488,595]</v>
+      </c>
+      <c r="C93">
+        <v>20</v>
+      </c>
+      <c r="D93">
+        <v>0</v>
+      </c>
+      <c r="E93">
+        <v>35</v>
+      </c>
+      <c r="F93">
+        <v>5</v>
+      </c>
+      <c r="G93">
+        <v>0</v>
+      </c>
+      <c r="H93">
+        <v>0</v>
+      </c>
+      <c r="I93">
+        <v>20</v>
+      </c>
+      <c r="J93">
+        <v>0</v>
+      </c>
+      <c r="K93">
+        <v>0</v>
+      </c>
+      <c r="L93">
+        <v>6</v>
+      </c>
+      <c r="M93">
+        <v>-20</v>
+      </c>
+      <c r="N93">
+        <v>0</v>
+      </c>
+      <c r="O93">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>94</v>
+      </c>
+      <c r="B94" t="str">
+        <v>["Product-188","East",276,384,492,600]</v>
+      </c>
+      <c r="C94">
+        <v>20</v>
+      </c>
+      <c r="D94">
+        <v>0</v>
+      </c>
+      <c r="E94">
+        <v>35</v>
+      </c>
+      <c r="F94">
+        <v>5</v>
+      </c>
+      <c r="G94">
+        <v>0</v>
+      </c>
+      <c r="H94">
+        <v>0</v>
+      </c>
+      <c r="I94">
+        <v>20</v>
+      </c>
+      <c r="J94">
+        <v>0</v>
+      </c>
+      <c r="K94">
+        <v>0</v>
+      </c>
+      <c r="L94">
+        <v>6</v>
+      </c>
+      <c r="M94">
+        <v>-20</v>
+      </c>
+      <c r="N94">
+        <v>0</v>
+      </c>
+      <c r="O94">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>95</v>
+      </c>
+      <c r="B95" t="str">
+        <v>["Product-189","West",278,387,496,605]</v>
+      </c>
+      <c r="C95">
+        <v>20</v>
+      </c>
+      <c r="D95">
+        <v>0</v>
+      </c>
+      <c r="E95">
+        <v>35</v>
+      </c>
+      <c r="F95">
+        <v>5</v>
+      </c>
+      <c r="G95">
+        <v>0</v>
+      </c>
+      <c r="H95">
+        <v>0</v>
+      </c>
+      <c r="I95">
+        <v>20</v>
+      </c>
+      <c r="J95">
+        <v>0</v>
+      </c>
+      <c r="K95">
+        <v>0</v>
+      </c>
+      <c r="L95">
+        <v>6</v>
+      </c>
+      <c r="M95">
+        <v>-20</v>
+      </c>
+      <c r="N95">
+        <v>0</v>
+      </c>
+      <c r="O95">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>96</v>
+      </c>
+      <c r="B96" t="str">
+        <v>["Product-190","East",280,390,500,610]</v>
+      </c>
+      <c r="C96">
+        <v>20</v>
+      </c>
+      <c r="D96">
+        <v>0</v>
+      </c>
+      <c r="E96">
+        <v>35</v>
+      </c>
+      <c r="F96">
+        <v>5</v>
+      </c>
+      <c r="G96">
+        <v>0</v>
+      </c>
+      <c r="H96">
+        <v>0</v>
+      </c>
+      <c r="I96">
+        <v>20</v>
+      </c>
+      <c r="J96">
+        <v>0</v>
+      </c>
+      <c r="K96">
+        <v>0</v>
+      </c>
+      <c r="L96">
+        <v>6</v>
+      </c>
+      <c r="M96">
+        <v>-20</v>
+      </c>
+      <c r="N96">
+        <v>0</v>
+      </c>
+      <c r="O96">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>97</v>
+      </c>
+      <c r="B97" t="str">
+        <v>["Product-191","West",282,393,504,615]</v>
+      </c>
+      <c r="C97">
+        <v>20</v>
+      </c>
+      <c r="D97">
+        <v>0</v>
+      </c>
+      <c r="E97">
+        <v>35</v>
+      </c>
+      <c r="F97">
+        <v>5</v>
+      </c>
+      <c r="G97">
+        <v>0</v>
+      </c>
+      <c r="H97">
+        <v>0</v>
+      </c>
+      <c r="I97">
+        <v>20</v>
+      </c>
+      <c r="J97">
+        <v>0</v>
+      </c>
+      <c r="K97">
+        <v>0</v>
+      </c>
+      <c r="L97">
+        <v>6</v>
+      </c>
+      <c r="M97">
+        <v>-20</v>
+      </c>
+      <c r="N97">
+        <v>0</v>
+      </c>
+      <c r="O97">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>98</v>
+      </c>
+      <c r="B98" t="str">
+        <v>["Product-192","East",284,396,508,620]</v>
+      </c>
+      <c r="C98">
+        <v>20</v>
+      </c>
+      <c r="D98">
+        <v>0</v>
+      </c>
+      <c r="E98">
+        <v>35</v>
+      </c>
+      <c r="F98">
+        <v>5</v>
+      </c>
+      <c r="G98">
+        <v>0</v>
+      </c>
+      <c r="H98">
+        <v>0</v>
+      </c>
+      <c r="I98">
+        <v>20</v>
+      </c>
+      <c r="J98">
+        <v>0</v>
+      </c>
+      <c r="K98">
+        <v>0</v>
+      </c>
+      <c r="L98">
+        <v>6</v>
+      </c>
+      <c r="M98">
+        <v>-20</v>
+      </c>
+      <c r="N98">
+        <v>0</v>
+      </c>
+      <c r="O98">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>99</v>
+      </c>
+      <c r="B99" t="str">
+        <v>["Product-193","West",286,399,512,625]</v>
+      </c>
+      <c r="C99">
+        <v>20</v>
+      </c>
+      <c r="D99">
+        <v>0</v>
+      </c>
+      <c r="E99">
+        <v>35</v>
+      </c>
+      <c r="F99">
+        <v>5</v>
+      </c>
+      <c r="G99">
+        <v>0</v>
+      </c>
+      <c r="H99">
+        <v>0</v>
+      </c>
+      <c r="I99">
+        <v>20</v>
+      </c>
+      <c r="J99">
+        <v>0</v>
+      </c>
+      <c r="K99">
+        <v>0</v>
+      </c>
+      <c r="L99">
+        <v>6</v>
+      </c>
+      <c r="M99">
+        <v>-20</v>
+      </c>
+      <c r="N99">
+        <v>0</v>
+      </c>
+      <c r="O99">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>100</v>
+      </c>
+      <c r="B100" t="str">
+        <v>["Product-194","East",288,402,516,630]</v>
+      </c>
+      <c r="C100">
+        <v>20</v>
+      </c>
+      <c r="D100">
+        <v>0</v>
+      </c>
+      <c r="E100">
+        <v>35</v>
+      </c>
+      <c r="F100">
+        <v>5</v>
+      </c>
+      <c r="G100">
+        <v>0</v>
+      </c>
+      <c r="H100">
+        <v>0</v>
+      </c>
+      <c r="I100">
+        <v>20</v>
+      </c>
+      <c r="J100">
+        <v>0</v>
+      </c>
+      <c r="K100">
+        <v>0</v>
+      </c>
+      <c r="L100">
+        <v>6</v>
+      </c>
+      <c r="M100">
+        <v>-20</v>
+      </c>
+      <c r="N100">
+        <v>0</v>
+      </c>
+      <c r="O100">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>101</v>
+      </c>
+      <c r="B101" t="str">
+        <v>["Product-195","West",290,405,520,635]</v>
+      </c>
+      <c r="C101">
+        <v>20</v>
+      </c>
+      <c r="D101">
+        <v>0</v>
+      </c>
+      <c r="E101">
+        <v>35</v>
+      </c>
+      <c r="F101">
+        <v>5</v>
+      </c>
+      <c r="G101">
+        <v>0</v>
+      </c>
+      <c r="H101">
+        <v>0</v>
+      </c>
+      <c r="I101">
+        <v>20</v>
+      </c>
+      <c r="J101">
+        <v>0</v>
+      </c>
+      <c r="K101">
+        <v>0</v>
+      </c>
+      <c r="L101">
+        <v>6</v>
+      </c>
+      <c r="M101">
+        <v>-20</v>
+      </c>
+      <c r="N101">
+        <v>0</v>
+      </c>
+      <c r="O101">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102">
+        <v>102</v>
+      </c>
+      <c r="B102" t="str">
+        <v>["Product-196","East",292,408,524,640]</v>
+      </c>
+      <c r="C102">
+        <v>20</v>
+      </c>
+      <c r="D102">
+        <v>0</v>
+      </c>
+      <c r="E102">
+        <v>35</v>
+      </c>
+      <c r="F102">
+        <v>5</v>
+      </c>
+      <c r="G102">
+        <v>0</v>
+      </c>
+      <c r="H102">
+        <v>0</v>
+      </c>
+      <c r="I102">
+        <v>20</v>
+      </c>
+      <c r="J102">
+        <v>0</v>
+      </c>
+      <c r="K102">
+        <v>0</v>
+      </c>
+      <c r="L102">
+        <v>6</v>
+      </c>
+      <c r="M102">
+        <v>-20</v>
+      </c>
+      <c r="N102">
+        <v>0</v>
+      </c>
+      <c r="O102">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103">
+        <v>103</v>
+      </c>
+      <c r="B103" t="str">
+        <v>["Product-197","West",294,411,528,645]</v>
+      </c>
+      <c r="C103">
+        <v>20</v>
+      </c>
+      <c r="D103">
+        <v>0</v>
+      </c>
+      <c r="E103">
+        <v>35</v>
+      </c>
+      <c r="F103">
+        <v>5</v>
+      </c>
+      <c r="G103">
+        <v>0</v>
+      </c>
+      <c r="H103">
+        <v>0</v>
+      </c>
+      <c r="I103">
+        <v>20</v>
+      </c>
+      <c r="J103">
+        <v>0</v>
+      </c>
+      <c r="K103">
+        <v>0</v>
+      </c>
+      <c r="L103">
+        <v>6</v>
+      </c>
+      <c r="M103">
+        <v>-20</v>
+      </c>
+      <c r="N103">
+        <v>0</v>
+      </c>
+      <c r="O103">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104">
+        <v>104</v>
+      </c>
+      <c r="B104" t="str">
+        <v>["Product-198","East",296,414,532,650]</v>
+      </c>
+      <c r="C104">
+        <v>20</v>
+      </c>
+      <c r="D104">
+        <v>0</v>
+      </c>
+      <c r="E104">
+        <v>35</v>
+      </c>
+      <c r="F104">
+        <v>5</v>
+      </c>
+      <c r="G104">
+        <v>0</v>
+      </c>
+      <c r="H104">
+        <v>0</v>
+      </c>
+      <c r="I104">
+        <v>20</v>
+      </c>
+      <c r="J104">
+        <v>0</v>
+      </c>
+      <c r="K104">
+        <v>0</v>
+      </c>
+      <c r="L104">
+        <v>6</v>
+      </c>
+      <c r="M104">
+        <v>-20</v>
+      </c>
+      <c r="N104">
+        <v>0</v>
+      </c>
+      <c r="O104">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105">
+        <v>105</v>
+      </c>
+      <c r="B105" t="str">
+        <v>["Product-199","West",298,417,536,655]</v>
+      </c>
+      <c r="C105">
+        <v>20</v>
+      </c>
+      <c r="D105">
+        <v>0</v>
+      </c>
+      <c r="E105">
+        <v>35</v>
+      </c>
+      <c r="F105">
+        <v>5</v>
+      </c>
+      <c r="G105">
+        <v>0</v>
+      </c>
+      <c r="H105">
+        <v>0</v>
+      </c>
+      <c r="I105">
+        <v>20</v>
+      </c>
+      <c r="J105">
+        <v>0</v>
+      </c>
+      <c r="K105">
+        <v>0</v>
+      </c>
+      <c r="L105">
+        <v>6</v>
+      </c>
+      <c r="M105">
+        <v>-20</v>
+      </c>
+      <c r="N105">
+        <v>0</v>
+      </c>
+      <c r="O105">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106">
+        <v>106</v>
+      </c>
+      <c r="B106" t="str">
+        <v>["Product-200","East",300,420,540,660]</v>
+      </c>
+      <c r="C106">
+        <v>20</v>
+      </c>
+      <c r="D106">
+        <v>0</v>
+      </c>
+      <c r="E106">
+        <v>35</v>
+      </c>
+      <c r="F106">
+        <v>5</v>
+      </c>
+      <c r="G106">
+        <v>0</v>
+      </c>
+      <c r="H106">
+        <v>0</v>
+      </c>
+      <c r="I106">
+        <v>20</v>
+      </c>
+      <c r="J106">
+        <v>0</v>
+      </c>
+      <c r="K106">
+        <v>0</v>
+      </c>
+      <c r="L106">
+        <v>6</v>
+      </c>
+      <c r="M106">
+        <v>-20</v>
+      </c>
+      <c r="N106">
+        <v>0</v>
+      </c>
+      <c r="O106">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107">
+        <v>107</v>
+      </c>
+      <c r="B107" t="str">
+        <v>["Product-201","West",302,423,544,665]</v>
+      </c>
+      <c r="C107">
+        <v>20</v>
+      </c>
+      <c r="D107">
+        <v>0</v>
+      </c>
+      <c r="E107">
+        <v>35</v>
+      </c>
+      <c r="F107">
+        <v>5</v>
+      </c>
+      <c r="G107">
+        <v>0</v>
+      </c>
+      <c r="H107">
+        <v>0</v>
+      </c>
+      <c r="I107">
+        <v>20</v>
+      </c>
+      <c r="J107">
+        <v>0</v>
+      </c>
+      <c r="K107">
+        <v>0</v>
+      </c>
+      <c r="L107">
+        <v>6</v>
+      </c>
+      <c r="M107">
+        <v>-20</v>
+      </c>
+      <c r="N107">
+        <v>0</v>
+      </c>
+      <c r="O107">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108">
+        <v>108</v>
+      </c>
+      <c r="B108" t="str">
+        <v>["Product-202","East",304,426,548,670]</v>
+      </c>
+      <c r="C108">
+        <v>20</v>
+      </c>
+      <c r="D108">
+        <v>0</v>
+      </c>
+      <c r="E108">
+        <v>35</v>
+      </c>
+      <c r="F108">
+        <v>5</v>
+      </c>
+      <c r="G108">
+        <v>0</v>
+      </c>
+      <c r="H108">
+        <v>0</v>
+      </c>
+      <c r="I108">
+        <v>20</v>
+      </c>
+      <c r="J108">
+        <v>0</v>
+      </c>
+      <c r="K108">
+        <v>0</v>
+      </c>
+      <c r="L108">
+        <v>6</v>
+      </c>
+      <c r="M108">
+        <v>-20</v>
+      </c>
+      <c r="N108">
+        <v>0</v>
+      </c>
+      <c r="O108">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109">
+        <v>109</v>
+      </c>
+      <c r="B109" t="str">
+        <v>["Product-203","West",306,429,552,675]</v>
+      </c>
+      <c r="C109">
+        <v>20</v>
+      </c>
+      <c r="D109">
+        <v>0</v>
+      </c>
+      <c r="E109">
+        <v>35</v>
+      </c>
+      <c r="F109">
+        <v>5</v>
+      </c>
+      <c r="G109">
+        <v>0</v>
+      </c>
+      <c r="H109">
+        <v>0</v>
+      </c>
+      <c r="I109">
+        <v>20</v>
+      </c>
+      <c r="J109">
+        <v>0</v>
+      </c>
+      <c r="K109">
+        <v>0</v>
+      </c>
+      <c r="L109">
+        <v>6</v>
+      </c>
+      <c r="M109">
+        <v>-20</v>
+      </c>
+      <c r="N109">
+        <v>0</v>
+      </c>
+      <c r="O109">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110">
+        <v>110</v>
+      </c>
+      <c r="B110" t="str">
+        <v>["Product-204","East",308,432,556,680]</v>
+      </c>
+      <c r="C110">
+        <v>20</v>
+      </c>
+      <c r="D110">
+        <v>0</v>
+      </c>
+      <c r="E110">
+        <v>35</v>
+      </c>
+      <c r="F110">
+        <v>5</v>
+      </c>
+      <c r="G110">
+        <v>0</v>
+      </c>
+      <c r="H110">
+        <v>0</v>
+      </c>
+      <c r="I110">
+        <v>20</v>
+      </c>
+      <c r="J110">
+        <v>0</v>
+      </c>
+      <c r="K110">
+        <v>0</v>
+      </c>
+      <c r="L110">
+        <v>6</v>
+      </c>
+      <c r="M110">
+        <v>-20</v>
+      </c>
+      <c r="N110">
+        <v>0</v>
+      </c>
+      <c r="O110">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111">
+        <v>111</v>
+      </c>
+      <c r="B111" t="str">
+        <v>["Product-205","West",310,435,560,685]</v>
+      </c>
+      <c r="C111">
+        <v>20</v>
+      </c>
+      <c r="D111">
+        <v>0</v>
+      </c>
+      <c r="E111">
+        <v>35</v>
+      </c>
+      <c r="F111">
+        <v>5</v>
+      </c>
+      <c r="G111">
+        <v>0</v>
+      </c>
+      <c r="H111">
+        <v>0</v>
+      </c>
+      <c r="I111">
+        <v>20</v>
+      </c>
+      <c r="J111">
+        <v>0</v>
+      </c>
+      <c r="K111">
+        <v>0</v>
+      </c>
+      <c r="L111">
+        <v>6</v>
+      </c>
+      <c r="M111">
+        <v>-20</v>
+      </c>
+      <c r="N111">
+        <v>0</v>
+      </c>
+      <c r="O111">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112">
+        <v>112</v>
+      </c>
+      <c r="B112" t="str">
+        <v>["Product-206","East",312,438,564,690]</v>
+      </c>
+      <c r="C112">
+        <v>20</v>
+      </c>
+      <c r="D112">
+        <v>0</v>
+      </c>
+      <c r="E112">
+        <v>35</v>
+      </c>
+      <c r="F112">
+        <v>5</v>
+      </c>
+      <c r="G112">
+        <v>0</v>
+      </c>
+      <c r="H112">
+        <v>0</v>
+      </c>
+      <c r="I112">
+        <v>20</v>
+      </c>
+      <c r="J112">
+        <v>0</v>
+      </c>
+      <c r="K112">
+        <v>0</v>
+      </c>
+      <c r="L112">
+        <v>6</v>
+      </c>
+      <c r="M112">
+        <v>-20</v>
+      </c>
+      <c r="N112">
+        <v>0</v>
+      </c>
+      <c r="O112">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113">
+        <v>113</v>
+      </c>
+      <c r="B113" t="str">
+        <v>["Product-207","West",314,441,568,695]</v>
+      </c>
+      <c r="C113">
+        <v>20</v>
+      </c>
+      <c r="D113">
+        <v>0</v>
+      </c>
+      <c r="E113">
+        <v>35</v>
+      </c>
+      <c r="F113">
+        <v>5</v>
+      </c>
+      <c r="G113">
+        <v>0</v>
+      </c>
+      <c r="H113">
+        <v>0</v>
+      </c>
+      <c r="I113">
+        <v>20</v>
+      </c>
+      <c r="J113">
+        <v>0</v>
+      </c>
+      <c r="K113">
+        <v>0</v>
+      </c>
+      <c r="L113">
+        <v>6</v>
+      </c>
+      <c r="M113">
+        <v>-20</v>
+      </c>
+      <c r="N113">
+        <v>0</v>
+      </c>
+      <c r="O113">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114">
+        <v>114</v>
+      </c>
+      <c r="B114" t="str">
+        <v>["Product-208","East",316,444,572,700]</v>
+      </c>
+      <c r="C114">
+        <v>20</v>
+      </c>
+      <c r="D114">
+        <v>0</v>
+      </c>
+      <c r="E114">
+        <v>35</v>
+      </c>
+      <c r="F114">
+        <v>5</v>
+      </c>
+      <c r="G114">
+        <v>0</v>
+      </c>
+      <c r="H114">
+        <v>0</v>
+      </c>
+      <c r="I114">
+        <v>20</v>
+      </c>
+      <c r="J114">
+        <v>0</v>
+      </c>
+      <c r="K114">
+        <v>0</v>
+      </c>
+      <c r="L114">
+        <v>6</v>
+      </c>
+      <c r="M114">
+        <v>-20</v>
+      </c>
+      <c r="N114">
+        <v>0</v>
+      </c>
+      <c r="O114">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115">
+        <v>115</v>
+      </c>
+      <c r="B115" t="str">
+        <v>["Product-209","West",318,447,576,705]</v>
+      </c>
+      <c r="C115">
+        <v>20</v>
+      </c>
+      <c r="D115">
+        <v>0</v>
+      </c>
+      <c r="E115">
+        <v>35</v>
+      </c>
+      <c r="F115">
+        <v>5</v>
+      </c>
+      <c r="G115">
+        <v>0</v>
+      </c>
+      <c r="H115">
+        <v>0</v>
+      </c>
+      <c r="I115">
+        <v>20</v>
+      </c>
+      <c r="J115">
+        <v>0</v>
+      </c>
+      <c r="K115">
+        <v>0</v>
+      </c>
+      <c r="L115">
+        <v>6</v>
+      </c>
+      <c r="M115">
+        <v>-20</v>
+      </c>
+      <c r="N115">
+        <v>0</v>
+      </c>
+      <c r="O115">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116">
+        <v>116</v>
+      </c>
+      <c r="B116" t="str">
+        <v>["Product-210","East",320,450,580,710]</v>
+      </c>
+      <c r="C116">
+        <v>20</v>
+      </c>
+      <c r="D116">
+        <v>0</v>
+      </c>
+      <c r="E116">
+        <v>35</v>
+      </c>
+      <c r="F116">
+        <v>5</v>
+      </c>
+      <c r="G116">
+        <v>0</v>
+      </c>
+      <c r="H116">
+        <v>0</v>
+      </c>
+      <c r="I116">
+        <v>20</v>
+      </c>
+      <c r="J116">
+        <v>0</v>
+      </c>
+      <c r="K116">
+        <v>0</v>
+      </c>
+      <c r="L116">
+        <v>6</v>
+      </c>
+      <c r="M116">
+        <v>-20</v>
+      </c>
+      <c r="N116">
+        <v>0</v>
+      </c>
+      <c r="O116">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117">
+        <v>117</v>
+      </c>
+      <c r="B117" t="str">
+        <v>["Product-211","West",322,453,584,715]</v>
+      </c>
+      <c r="C117">
+        <v>20</v>
+      </c>
+      <c r="D117">
+        <v>0</v>
+      </c>
+      <c r="E117">
+        <v>35</v>
+      </c>
+      <c r="F117">
+        <v>5</v>
+      </c>
+      <c r="G117">
+        <v>0</v>
+      </c>
+      <c r="H117">
+        <v>0</v>
+      </c>
+      <c r="I117">
+        <v>20</v>
+      </c>
+      <c r="J117">
+        <v>0</v>
+      </c>
+      <c r="K117">
+        <v>0</v>
+      </c>
+      <c r="L117">
+        <v>6</v>
+      </c>
+      <c r="M117">
+        <v>-20</v>
+      </c>
+      <c r="N117">
+        <v>0</v>
+      </c>
+      <c r="O117">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118">
+        <v>118</v>
+      </c>
+      <c r="B118" t="str">
+        <v>["Product-212","East",324,456,588,720]</v>
+      </c>
+      <c r="C118">
+        <v>20</v>
+      </c>
+      <c r="D118">
+        <v>0</v>
+      </c>
+      <c r="E118">
+        <v>35</v>
+      </c>
+      <c r="F118">
+        <v>5</v>
+      </c>
+      <c r="G118">
+        <v>0</v>
+      </c>
+      <c r="H118">
+        <v>0</v>
+      </c>
+      <c r="I118">
+        <v>20</v>
+      </c>
+      <c r="J118">
+        <v>0</v>
+      </c>
+      <c r="K118">
+        <v>0</v>
+      </c>
+      <c r="L118">
+        <v>6</v>
+      </c>
+      <c r="M118">
+        <v>-20</v>
+      </c>
+      <c r="N118">
+        <v>0</v>
+      </c>
+      <c r="O118">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119">
+        <v>119</v>
+      </c>
+      <c r="B119" t="str">
+        <v>["Product-213","West",326,459,592,725]</v>
+      </c>
+      <c r="C119">
+        <v>20</v>
+      </c>
+      <c r="D119">
+        <v>0</v>
+      </c>
+      <c r="E119">
+        <v>35</v>
+      </c>
+      <c r="F119">
+        <v>5</v>
+      </c>
+      <c r="G119">
+        <v>0</v>
+      </c>
+      <c r="H119">
+        <v>0</v>
+      </c>
+      <c r="I119">
+        <v>20</v>
+      </c>
+      <c r="J119">
+        <v>0</v>
+      </c>
+      <c r="K119">
+        <v>0</v>
+      </c>
+      <c r="L119">
+        <v>6</v>
+      </c>
+      <c r="M119">
+        <v>-20</v>
+      </c>
+      <c r="N119">
+        <v>0</v>
+      </c>
+      <c r="O119">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120">
+        <v>120</v>
+      </c>
+      <c r="B120" t="str">
+        <v>["Product-214","East",328,462,596,730]</v>
+      </c>
+      <c r="C120">
+        <v>20</v>
+      </c>
+      <c r="D120">
+        <v>0</v>
+      </c>
+      <c r="E120">
+        <v>35</v>
+      </c>
+      <c r="F120">
+        <v>5</v>
+      </c>
+      <c r="G120">
+        <v>0</v>
+      </c>
+      <c r="H120">
+        <v>0</v>
+      </c>
+      <c r="I120">
+        <v>20</v>
+      </c>
+      <c r="J120">
+        <v>0</v>
+      </c>
+      <c r="K120">
+        <v>0</v>
+      </c>
+      <c r="L120">
+        <v>6</v>
+      </c>
+      <c r="M120">
+        <v>-20</v>
+      </c>
+      <c r="N120">
+        <v>0</v>
+      </c>
+      <c r="O120">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121">
+        <v>121</v>
+      </c>
+      <c r="B121" t="str">
+        <v>["Product-215","West",330,465,600,735]</v>
+      </c>
+      <c r="C121">
+        <v>20</v>
+      </c>
+      <c r="D121">
+        <v>0</v>
+      </c>
+      <c r="E121">
+        <v>35</v>
+      </c>
+      <c r="F121">
+        <v>5</v>
+      </c>
+      <c r="G121">
+        <v>0</v>
+      </c>
+      <c r="H121">
+        <v>0</v>
+      </c>
+      <c r="I121">
+        <v>20</v>
+      </c>
+      <c r="J121">
+        <v>0</v>
+      </c>
+      <c r="K121">
+        <v>0</v>
+      </c>
+      <c r="L121">
+        <v>6</v>
+      </c>
+      <c r="M121">
+        <v>-20</v>
+      </c>
+      <c r="N121">
+        <v>0</v>
+      </c>
+      <c r="O121">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122">
+        <v>122</v>
+      </c>
+      <c r="B122" t="str">
+        <v>["Product-216","East",332,468,604,740]</v>
+      </c>
+      <c r="C122">
+        <v>20</v>
+      </c>
+      <c r="D122">
+        <v>0</v>
+      </c>
+      <c r="E122">
+        <v>35</v>
+      </c>
+      <c r="F122">
+        <v>5</v>
+      </c>
+      <c r="G122">
+        <v>0</v>
+      </c>
+      <c r="H122">
+        <v>0</v>
+      </c>
+      <c r="I122">
+        <v>20</v>
+      </c>
+      <c r="J122">
+        <v>0</v>
+      </c>
+      <c r="K122">
+        <v>0</v>
+      </c>
+      <c r="L122">
+        <v>6</v>
+      </c>
+      <c r="M122">
+        <v>-20</v>
+      </c>
+      <c r="N122">
+        <v>0</v>
+      </c>
+      <c r="O122">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123">
+        <v>123</v>
+      </c>
+      <c r="B123" t="str">
+        <v>["Product-217","West",334,471,608,745]</v>
+      </c>
+      <c r="C123">
+        <v>20</v>
+      </c>
+      <c r="D123">
+        <v>0</v>
+      </c>
+      <c r="E123">
+        <v>35</v>
+      </c>
+      <c r="F123">
+        <v>5</v>
+      </c>
+      <c r="G123">
+        <v>0</v>
+      </c>
+      <c r="H123">
+        <v>0</v>
+      </c>
+      <c r="I123">
+        <v>20</v>
+      </c>
+      <c r="J123">
+        <v>0</v>
+      </c>
+      <c r="K123">
+        <v>0</v>
+      </c>
+      <c r="L123">
+        <v>6</v>
+      </c>
+      <c r="M123">
+        <v>-20</v>
+      </c>
+      <c r="N123">
+        <v>0</v>
+      </c>
+      <c r="O123">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124">
+        <v>124</v>
+      </c>
+      <c r="B124" t="str">
+        <v>["Product-218","East",336,474,612,750]</v>
+      </c>
+      <c r="C124">
+        <v>20</v>
+      </c>
+      <c r="D124">
+        <v>0</v>
+      </c>
+      <c r="E124">
+        <v>35</v>
+      </c>
+      <c r="F124">
+        <v>5</v>
+      </c>
+      <c r="G124">
+        <v>0</v>
+      </c>
+      <c r="H124">
+        <v>0</v>
+      </c>
+      <c r="I124">
+        <v>20</v>
+      </c>
+      <c r="J124">
+        <v>0</v>
+      </c>
+      <c r="K124">
+        <v>0</v>
+      </c>
+      <c r="L124">
+        <v>6</v>
+      </c>
+      <c r="M124">
+        <v>-20</v>
+      </c>
+      <c r="N124">
+        <v>0</v>
+      </c>
+      <c r="O124">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125">
+        <v>125</v>
+      </c>
+      <c r="B125" t="str">
+        <v>["Product-219","West",338,477,616,755]</v>
+      </c>
+      <c r="C125">
+        <v>20</v>
+      </c>
+      <c r="D125">
+        <v>0</v>
+      </c>
+      <c r="E125">
+        <v>35</v>
+      </c>
+      <c r="F125">
+        <v>5</v>
+      </c>
+      <c r="G125">
+        <v>0</v>
+      </c>
+      <c r="H125">
+        <v>0</v>
+      </c>
+      <c r="I125">
+        <v>20</v>
+      </c>
+      <c r="J125">
+        <v>0</v>
+      </c>
+      <c r="K125">
+        <v>0</v>
+      </c>
+      <c r="L125">
+        <v>6</v>
+      </c>
+      <c r="M125">
+        <v>-20</v>
+      </c>
+      <c r="N125">
+        <v>0</v>
+      </c>
+      <c r="O125">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126">
+        <v>126</v>
+      </c>
+      <c r="B126" t="str">
+        <v>["Product-220","East",340,480,620,760]</v>
+      </c>
+      <c r="C126">
+        <v>20</v>
+      </c>
+      <c r="D126">
+        <v>0</v>
+      </c>
+      <c r="E126">
+        <v>35</v>
+      </c>
+      <c r="F126">
+        <v>5</v>
+      </c>
+      <c r="G126">
+        <v>0</v>
+      </c>
+      <c r="H126">
+        <v>0</v>
+      </c>
+      <c r="I126">
+        <v>20</v>
+      </c>
+      <c r="J126">
+        <v>0</v>
+      </c>
+      <c r="K126">
+        <v>0</v>
+      </c>
+      <c r="L126">
+        <v>6</v>
+      </c>
+      <c r="M126">
+        <v>-20</v>
+      </c>
+      <c r="N126">
+        <v>0</v>
+      </c>
+      <c r="O126">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127">
+        <v>127</v>
+      </c>
+      <c r="B127" t="str">
+        <v>["Product-221","West",342,483,624,765]</v>
+      </c>
+      <c r="C127">
+        <v>20</v>
+      </c>
+      <c r="D127">
+        <v>0</v>
+      </c>
+      <c r="E127">
+        <v>35</v>
+      </c>
+      <c r="F127">
+        <v>5</v>
+      </c>
+      <c r="G127">
+        <v>0</v>
+      </c>
+      <c r="H127">
+        <v>0</v>
+      </c>
+      <c r="I127">
+        <v>20</v>
+      </c>
+      <c r="J127">
+        <v>0</v>
+      </c>
+      <c r="K127">
+        <v>0</v>
+      </c>
+      <c r="L127">
+        <v>6</v>
+      </c>
+      <c r="M127">
+        <v>-20</v>
+      </c>
+      <c r="N127">
+        <v>0</v>
+      </c>
+      <c r="O127">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128">
+        <v>128</v>
+      </c>
+      <c r="B128" t="str">
+        <v>["Product-222","East",344,486,628,770]</v>
+      </c>
+      <c r="C128">
+        <v>20</v>
+      </c>
+      <c r="D128">
+        <v>0</v>
+      </c>
+      <c r="E128">
+        <v>35</v>
+      </c>
+      <c r="F128">
+        <v>5</v>
+      </c>
+      <c r="G128">
+        <v>0</v>
+      </c>
+      <c r="H128">
+        <v>0</v>
+      </c>
+      <c r="I128">
+        <v>20</v>
+      </c>
+      <c r="J128">
+        <v>0</v>
+      </c>
+      <c r="K128">
+        <v>0</v>
+      </c>
+      <c r="L128">
+        <v>6</v>
+      </c>
+      <c r="M128">
+        <v>-20</v>
+      </c>
+      <c r="N128">
+        <v>0</v>
+      </c>
+      <c r="O128">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129">
+        <v>129</v>
+      </c>
+      <c r="B129" t="str">
+        <v>["Product-223","West",346,489,632,775]</v>
+      </c>
+      <c r="C129">
+        <v>20</v>
+      </c>
+      <c r="D129">
+        <v>0</v>
+      </c>
+      <c r="E129">
+        <v>35</v>
+      </c>
+      <c r="F129">
+        <v>5</v>
+      </c>
+      <c r="G129">
+        <v>0</v>
+      </c>
+      <c r="H129">
+        <v>0</v>
+      </c>
+      <c r="I129">
+        <v>20</v>
+      </c>
+      <c r="J129">
+        <v>0</v>
+      </c>
+      <c r="K129">
+        <v>0</v>
+      </c>
+      <c r="L129">
+        <v>6</v>
+      </c>
+      <c r="M129">
+        <v>-20</v>
+      </c>
+      <c r="N129">
+        <v>0</v>
+      </c>
+      <c r="O129">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130">
+        <v>130</v>
+      </c>
+      <c r="B130" t="str">
+        <v>["Product-224","East",348,492,636,780]</v>
+      </c>
+      <c r="C130">
+        <v>20</v>
+      </c>
+      <c r="D130">
+        <v>0</v>
+      </c>
+      <c r="E130">
+        <v>35</v>
+      </c>
+      <c r="F130">
+        <v>5</v>
+      </c>
+      <c r="G130">
+        <v>0</v>
+      </c>
+      <c r="H130">
+        <v>0</v>
+      </c>
+      <c r="I130">
+        <v>20</v>
+      </c>
+      <c r="J130">
+        <v>0</v>
+      </c>
+      <c r="K130">
+        <v>0</v>
+      </c>
+      <c r="L130">
+        <v>6</v>
+      </c>
+      <c r="M130">
+        <v>-20</v>
+      </c>
+      <c r="N130">
+        <v>0</v>
+      </c>
+      <c r="O130">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131">
+        <v>131</v>
+      </c>
+      <c r="B131" t="str">
+        <v>["Product-225","West",350,495,640,785]</v>
+      </c>
+      <c r="C131">
+        <v>20</v>
+      </c>
+      <c r="D131">
+        <v>0</v>
+      </c>
+      <c r="E131">
+        <v>35</v>
+      </c>
+      <c r="F131">
+        <v>5</v>
+      </c>
+      <c r="G131">
+        <v>0</v>
+      </c>
+      <c r="H131">
+        <v>0</v>
+      </c>
+      <c r="I131">
+        <v>20</v>
+      </c>
+      <c r="J131">
+        <v>0</v>
+      </c>
+      <c r="K131">
+        <v>0</v>
+      </c>
+      <c r="L131">
+        <v>6</v>
+      </c>
+      <c r="M131">
+        <v>-20</v>
+      </c>
+      <c r="N131">
+        <v>0</v>
+      </c>
+      <c r="O131">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132">
+        <v>132</v>
+      </c>
+      <c r="B132" t="str">
+        <v>["Product-226","East",352,498,644,790]</v>
+      </c>
+      <c r="C132">
+        <v>20</v>
+      </c>
+      <c r="D132">
+        <v>0</v>
+      </c>
+      <c r="E132">
+        <v>35</v>
+      </c>
+      <c r="F132">
+        <v>5</v>
+      </c>
+      <c r="G132">
+        <v>0</v>
+      </c>
+      <c r="H132">
+        <v>0</v>
+      </c>
+      <c r="I132">
+        <v>20</v>
+      </c>
+      <c r="J132">
+        <v>0</v>
+      </c>
+      <c r="K132">
+        <v>0</v>
+      </c>
+      <c r="L132">
+        <v>6</v>
+      </c>
+      <c r="M132">
+        <v>-20</v>
+      </c>
+      <c r="N132">
+        <v>0</v>
+      </c>
+      <c r="O132">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133">
+        <v>133</v>
+      </c>
+      <c r="B133" t="str">
+        <v>["Product-227","West",354,501,648,795]</v>
+      </c>
+      <c r="C133">
+        <v>20</v>
+      </c>
+      <c r="D133">
+        <v>0</v>
+      </c>
+      <c r="E133">
+        <v>35</v>
+      </c>
+      <c r="F133">
+        <v>5</v>
+      </c>
+      <c r="G133">
+        <v>0</v>
+      </c>
+      <c r="H133">
+        <v>0</v>
+      </c>
+      <c r="I133">
+        <v>20</v>
+      </c>
+      <c r="J133">
+        <v>0</v>
+      </c>
+      <c r="K133">
+        <v>0</v>
+      </c>
+      <c r="L133">
+        <v>6</v>
+      </c>
+      <c r="M133">
+        <v>-20</v>
+      </c>
+      <c r="N133">
+        <v>0</v>
+      </c>
+      <c r="O133">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134">
+        <v>134</v>
+      </c>
+      <c r="B134" t="str">
+        <v>["Product-228","East",356,504,652,800]</v>
+      </c>
+      <c r="C134">
+        <v>20</v>
+      </c>
+      <c r="D134">
+        <v>0</v>
+      </c>
+      <c r="E134">
+        <v>35</v>
+      </c>
+      <c r="F134">
+        <v>5</v>
+      </c>
+      <c r="G134">
+        <v>0</v>
+      </c>
+      <c r="H134">
+        <v>0</v>
+      </c>
+      <c r="I134">
+        <v>20</v>
+      </c>
+      <c r="J134">
+        <v>0</v>
+      </c>
+      <c r="K134">
+        <v>0</v>
+      </c>
+      <c r="L134">
+        <v>6</v>
+      </c>
+      <c r="M134">
+        <v>-20</v>
+      </c>
+      <c r="N134">
+        <v>0</v>
+      </c>
+      <c r="O134">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135">
+        <v>135</v>
+      </c>
+      <c r="B135" t="str">
+        <v>["Product-229","West",358,507,656,805]</v>
+      </c>
+      <c r="C135">
+        <v>20</v>
+      </c>
+      <c r="D135">
+        <v>0</v>
+      </c>
+      <c r="E135">
+        <v>35</v>
+      </c>
+      <c r="F135">
+        <v>5</v>
+      </c>
+      <c r="G135">
+        <v>0</v>
+      </c>
+      <c r="H135">
+        <v>0</v>
+      </c>
+      <c r="I135">
+        <v>20</v>
+      </c>
+      <c r="J135">
+        <v>0</v>
+      </c>
+      <c r="K135">
+        <v>0</v>
+      </c>
+      <c r="L135">
+        <v>6</v>
+      </c>
+      <c r="M135">
+        <v>-20</v>
+      </c>
+      <c r="N135">
+        <v>0</v>
+      </c>
+      <c r="O135">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136">
+        <v>136</v>
+      </c>
+      <c r="B136" t="str">
+        <v>["Product-230","East",360,510,660,810]</v>
+      </c>
+      <c r="C136">
+        <v>20</v>
+      </c>
+      <c r="D136">
+        <v>0</v>
+      </c>
+      <c r="E136">
+        <v>35</v>
+      </c>
+      <c r="F136">
+        <v>5</v>
+      </c>
+      <c r="G136">
+        <v>0</v>
+      </c>
+      <c r="H136">
+        <v>0</v>
+      </c>
+      <c r="I136">
+        <v>20</v>
+      </c>
+      <c r="J136">
+        <v>0</v>
+      </c>
+      <c r="K136">
+        <v>0</v>
+      </c>
+      <c r="L136">
+        <v>6</v>
+      </c>
+      <c r="M136">
+        <v>-20</v>
+      </c>
+      <c r="N136">
+        <v>0</v>
+      </c>
+      <c r="O136">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137">
+        <v>137</v>
+      </c>
+      <c r="B137" t="str">
+        <v>["Product-231","West",362,513,664,815]</v>
+      </c>
+      <c r="C137">
+        <v>20</v>
+      </c>
+      <c r="D137">
+        <v>0</v>
+      </c>
+      <c r="E137">
+        <v>35</v>
+      </c>
+      <c r="F137">
+        <v>5</v>
+      </c>
+      <c r="G137">
+        <v>0</v>
+      </c>
+      <c r="H137">
+        <v>0</v>
+      </c>
+      <c r="I137">
+        <v>20</v>
+      </c>
+      <c r="J137">
+        <v>0</v>
+      </c>
+      <c r="K137">
+        <v>0</v>
+      </c>
+      <c r="L137">
+        <v>6</v>
+      </c>
+      <c r="M137">
+        <v>-20</v>
+      </c>
+      <c r="N137">
+        <v>0</v>
+      </c>
+      <c r="O137">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138">
+        <v>138</v>
+      </c>
+      <c r="B138" t="str">
+        <v>["Product-232","East",364,516,668,820]</v>
+      </c>
+      <c r="C138">
+        <v>20</v>
+      </c>
+      <c r="D138">
+        <v>0</v>
+      </c>
+      <c r="E138">
+        <v>35</v>
+      </c>
+      <c r="F138">
+        <v>5</v>
+      </c>
+      <c r="G138">
+        <v>0</v>
+      </c>
+      <c r="H138">
+        <v>0</v>
+      </c>
+      <c r="I138">
+        <v>20</v>
+      </c>
+      <c r="J138">
+        <v>0</v>
+      </c>
+      <c r="K138">
+        <v>0</v>
+      </c>
+      <c r="L138">
+        <v>6</v>
+      </c>
+      <c r="M138">
+        <v>-20</v>
+      </c>
+      <c r="N138">
+        <v>0</v>
+      </c>
+      <c r="O138">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139">
+        <v>139</v>
+      </c>
+      <c r="B139" t="str">
+        <v>["Product-233","West",366,519,672,825]</v>
+      </c>
+      <c r="C139">
+        <v>20</v>
+      </c>
+      <c r="D139">
+        <v>0</v>
+      </c>
+      <c r="E139">
+        <v>35</v>
+      </c>
+      <c r="F139">
+        <v>5</v>
+      </c>
+      <c r="G139">
+        <v>0</v>
+      </c>
+      <c r="H139">
+        <v>0</v>
+      </c>
+      <c r="I139">
+        <v>20</v>
+      </c>
+      <c r="J139">
+        <v>0</v>
+      </c>
+      <c r="K139">
+        <v>0</v>
+      </c>
+      <c r="L139">
+        <v>6</v>
+      </c>
+      <c r="M139">
+        <v>-20</v>
+      </c>
+      <c r="N139">
+        <v>0</v>
+      </c>
+      <c r="O139">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140">
+        <v>140</v>
+      </c>
+      <c r="B140" t="str">
+        <v>["Product-234","East",368,522,676,830]</v>
+      </c>
+      <c r="C140">
+        <v>20</v>
+      </c>
+      <c r="D140">
+        <v>0</v>
+      </c>
+      <c r="E140">
+        <v>35</v>
+      </c>
+      <c r="F140">
+        <v>5</v>
+      </c>
+      <c r="G140">
+        <v>0</v>
+      </c>
+      <c r="H140">
+        <v>0</v>
+      </c>
+      <c r="I140">
+        <v>20</v>
+      </c>
+      <c r="J140">
+        <v>0</v>
+      </c>
+      <c r="K140">
+        <v>0</v>
+      </c>
+      <c r="L140">
+        <v>6</v>
+      </c>
+      <c r="M140">
+        <v>-20</v>
+      </c>
+      <c r="N140">
+        <v>0</v>
+      </c>
+      <c r="O140">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141">
+        <v>141</v>
+      </c>
+      <c r="B141" t="str">
+        <v>["Product-235","West",370,525,680,835]</v>
+      </c>
+      <c r="C141">
+        <v>20</v>
+      </c>
+      <c r="D141">
+        <v>0</v>
+      </c>
+      <c r="E141">
+        <v>35</v>
+      </c>
+      <c r="F141">
+        <v>5</v>
+      </c>
+      <c r="G141">
+        <v>0</v>
+      </c>
+      <c r="H141">
+        <v>0</v>
+      </c>
+      <c r="I141">
+        <v>20</v>
+      </c>
+      <c r="J141">
+        <v>0</v>
+      </c>
+      <c r="K141">
+        <v>0</v>
+      </c>
+      <c r="L141">
+        <v>6</v>
+      </c>
+      <c r="M141">
+        <v>-20</v>
+      </c>
+      <c r="N141">
+        <v>0</v>
+      </c>
+      <c r="O141">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142">
+        <v>142</v>
+      </c>
+      <c r="B142" t="str">
+        <v>["Product-236","East",372,528,684,840]</v>
+      </c>
+      <c r="C142">
+        <v>20</v>
+      </c>
+      <c r="D142">
+        <v>0</v>
+      </c>
+      <c r="E142">
+        <v>35</v>
+      </c>
+      <c r="F142">
+        <v>5</v>
+      </c>
+      <c r="G142">
+        <v>0</v>
+      </c>
+      <c r="H142">
+        <v>0</v>
+      </c>
+      <c r="I142">
+        <v>20</v>
+      </c>
+      <c r="J142">
+        <v>0</v>
+      </c>
+      <c r="K142">
+        <v>0</v>
+      </c>
+      <c r="L142">
+        <v>6</v>
+      </c>
+      <c r="M142">
+        <v>-20</v>
+      </c>
+      <c r="N142">
+        <v>0</v>
+      </c>
+      <c r="O142">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143">
+        <v>143</v>
+      </c>
+      <c r="B143" t="str">
+        <v>["Product-237","West",374,531,688,845]</v>
+      </c>
+      <c r="C143">
+        <v>20</v>
+      </c>
+      <c r="D143">
+        <v>0</v>
+      </c>
+      <c r="E143">
+        <v>35</v>
+      </c>
+      <c r="F143">
+        <v>5</v>
+      </c>
+      <c r="G143">
+        <v>0</v>
+      </c>
+      <c r="H143">
+        <v>0</v>
+      </c>
+      <c r="I143">
+        <v>20</v>
+      </c>
+      <c r="J143">
+        <v>0</v>
+      </c>
+      <c r="K143">
+        <v>0</v>
+      </c>
+      <c r="L143">
+        <v>6</v>
+      </c>
+      <c r="M143">
+        <v>-20</v>
+      </c>
+      <c r="N143">
+        <v>0</v>
+      </c>
+      <c r="O143">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144">
+        <v>144</v>
+      </c>
+      <c r="B144" t="str">
+        <v>["Product-238","East",376,534,692,850]</v>
+      </c>
+      <c r="C144">
+        <v>20</v>
+      </c>
+      <c r="D144">
+        <v>0</v>
+      </c>
+      <c r="E144">
+        <v>35</v>
+      </c>
+      <c r="F144">
+        <v>5</v>
+      </c>
+      <c r="G144">
+        <v>0</v>
+      </c>
+      <c r="H144">
+        <v>0</v>
+      </c>
+      <c r="I144">
+        <v>20</v>
+      </c>
+      <c r="J144">
+        <v>0</v>
+      </c>
+      <c r="K144">
+        <v>0</v>
+      </c>
+      <c r="L144">
+        <v>6</v>
+      </c>
+      <c r="M144">
+        <v>-20</v>
+      </c>
+      <c r="N144">
+        <v>0</v>
+      </c>
+      <c r="O144">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145">
+        <v>145</v>
+      </c>
+      <c r="B145" t="str">
+        <v>["Product-239","West",378,537,696,855]</v>
+      </c>
+      <c r="C145">
+        <v>20</v>
+      </c>
+      <c r="D145">
+        <v>0</v>
+      </c>
+      <c r="E145">
+        <v>35</v>
+      </c>
+      <c r="F145">
+        <v>5</v>
+      </c>
+      <c r="G145">
+        <v>0</v>
+      </c>
+      <c r="H145">
+        <v>0</v>
+      </c>
+      <c r="I145">
+        <v>20</v>
+      </c>
+      <c r="J145">
+        <v>0</v>
+      </c>
+      <c r="K145">
+        <v>0</v>
+      </c>
+      <c r="L145">
+        <v>6</v>
+      </c>
+      <c r="M145">
+        <v>-20</v>
+      </c>
+      <c r="N145">
+        <v>0</v>
+      </c>
+      <c r="O145">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146">
+        <v>146</v>
+      </c>
+      <c r="B146" t="str">
+        <v>["Product-240","East",380,540,700,860]</v>
+      </c>
+      <c r="C146">
+        <v>20</v>
+      </c>
+      <c r="D146">
+        <v>0</v>
+      </c>
+      <c r="E146">
+        <v>35</v>
+      </c>
+      <c r="F146">
+        <v>5</v>
+      </c>
+      <c r="G146">
+        <v>0</v>
+      </c>
+      <c r="H146">
+        <v>0</v>
+      </c>
+      <c r="I146">
+        <v>20</v>
+      </c>
+      <c r="J146">
+        <v>0</v>
+      </c>
+      <c r="K146">
+        <v>0</v>
+      </c>
+      <c r="L146">
+        <v>6</v>
+      </c>
+      <c r="M146">
+        <v>-20</v>
+      </c>
+      <c r="N146">
+        <v>0</v>
+      </c>
+      <c r="O146">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147">
+        <v>147</v>
+      </c>
+      <c r="B147" t="str">
+        <v>["Product-241","West",382,543,704,865]</v>
+      </c>
+      <c r="C147">
+        <v>20</v>
+      </c>
+      <c r="D147">
+        <v>0</v>
+      </c>
+      <c r="E147">
+        <v>35</v>
+      </c>
+      <c r="F147">
+        <v>5</v>
+      </c>
+      <c r="G147">
+        <v>0</v>
+      </c>
+      <c r="H147">
+        <v>0</v>
+      </c>
+      <c r="I147">
+        <v>20</v>
+      </c>
+      <c r="J147">
+        <v>0</v>
+      </c>
+      <c r="K147">
+        <v>0</v>
+      </c>
+      <c r="L147">
+        <v>6</v>
+      </c>
+      <c r="M147">
+        <v>-20</v>
+      </c>
+      <c r="N147">
+        <v>0</v>
+      </c>
+      <c r="O147">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148">
+        <v>148</v>
+      </c>
+      <c r="B148" t="str">
+        <v>["Product-242","East",384,546,708,870]</v>
+      </c>
+      <c r="C148">
+        <v>20</v>
+      </c>
+      <c r="D148">
+        <v>0</v>
+      </c>
+      <c r="E148">
+        <v>35</v>
+      </c>
+      <c r="F148">
+        <v>5</v>
+      </c>
+      <c r="G148">
+        <v>0</v>
+      </c>
+      <c r="H148">
+        <v>0</v>
+      </c>
+      <c r="I148">
+        <v>20</v>
+      </c>
+      <c r="J148">
+        <v>0</v>
+      </c>
+      <c r="K148">
+        <v>0</v>
+      </c>
+      <c r="L148">
+        <v>6</v>
+      </c>
+      <c r="M148">
+        <v>-20</v>
+      </c>
+      <c r="N148">
+        <v>0</v>
+      </c>
+      <c r="O148">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149">
+        <v>149</v>
+      </c>
+      <c r="B149" t="str">
+        <v>["Product-243","West",386,549,712,875]</v>
+      </c>
+      <c r="C149">
+        <v>20</v>
+      </c>
+      <c r="D149">
+        <v>0</v>
+      </c>
+      <c r="E149">
+        <v>35</v>
+      </c>
+      <c r="F149">
+        <v>5</v>
+      </c>
+      <c r="G149">
+        <v>0</v>
+      </c>
+      <c r="H149">
+        <v>0</v>
+      </c>
+      <c r="I149">
+        <v>20</v>
+      </c>
+      <c r="J149">
+        <v>0</v>
+      </c>
+      <c r="K149">
+        <v>0</v>
+      </c>
+      <c r="L149">
+        <v>6</v>
+      </c>
+      <c r="M149">
+        <v>-20</v>
+      </c>
+      <c r="N149">
+        <v>0</v>
+      </c>
+      <c r="O149">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150">
+        <v>150</v>
+      </c>
+      <c r="B150" t="str">
+        <v>["Product-244","East",388,552,716,880]</v>
+      </c>
+      <c r="C150">
+        <v>20</v>
+      </c>
+      <c r="D150">
+        <v>0</v>
+      </c>
+      <c r="E150">
+        <v>35</v>
+      </c>
+      <c r="F150">
+        <v>5</v>
+      </c>
+      <c r="G150">
+        <v>0</v>
+      </c>
+      <c r="H150">
+        <v>0</v>
+      </c>
+      <c r="I150">
+        <v>20</v>
+      </c>
+      <c r="J150">
+        <v>0</v>
+      </c>
+      <c r="K150">
+        <v>0</v>
+      </c>
+      <c r="L150">
+        <v>6</v>
+      </c>
+      <c r="M150">
+        <v>-20</v>
+      </c>
+      <c r="N150">
+        <v>0</v>
+      </c>
+      <c r="O150">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151">
+        <v>151</v>
+      </c>
+      <c r="B151" t="str">
+        <v>["Product-245","West",390,555,720,885]</v>
+      </c>
+      <c r="C151">
+        <v>20</v>
+      </c>
+      <c r="D151">
+        <v>0</v>
+      </c>
+      <c r="E151">
+        <v>35</v>
+      </c>
+      <c r="F151">
+        <v>5</v>
+      </c>
+      <c r="G151">
+        <v>0</v>
+      </c>
+      <c r="H151">
+        <v>0</v>
+      </c>
+      <c r="I151">
+        <v>20</v>
+      </c>
+      <c r="J151">
+        <v>0</v>
+      </c>
+      <c r="K151">
+        <v>0</v>
+      </c>
+      <c r="L151">
+        <v>6</v>
+      </c>
+      <c r="M151">
+        <v>-20</v>
+      </c>
+      <c r="N151">
+        <v>0</v>
+      </c>
+      <c r="O151">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152">
+        <v>152</v>
+      </c>
+      <c r="B152" t="str">
+        <v>["Product-246","East",392,558,724,890]</v>
+      </c>
+      <c r="C152">
+        <v>20</v>
+      </c>
+      <c r="D152">
+        <v>0</v>
+      </c>
+      <c r="E152">
+        <v>35</v>
+      </c>
+      <c r="F152">
+        <v>5</v>
+      </c>
+      <c r="G152">
+        <v>0</v>
+      </c>
+      <c r="H152">
+        <v>0</v>
+      </c>
+      <c r="I152">
+        <v>20</v>
+      </c>
+      <c r="J152">
+        <v>0</v>
+      </c>
+      <c r="K152">
+        <v>0</v>
+      </c>
+      <c r="L152">
+        <v>6</v>
+      </c>
+      <c r="M152">
+        <v>-20</v>
+      </c>
+      <c r="N152">
+        <v>0</v>
+      </c>
+      <c r="O152">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153">
+        <v>153</v>
+      </c>
+      <c r="B153" t="str">
+        <v>["Product-247","West",394,561,728,895]</v>
+      </c>
+      <c r="C153">
+        <v>20</v>
+      </c>
+      <c r="D153">
+        <v>0</v>
+      </c>
+      <c r="E153">
+        <v>35</v>
+      </c>
+      <c r="F153">
+        <v>5</v>
+      </c>
+      <c r="G153">
+        <v>0</v>
+      </c>
+      <c r="H153">
+        <v>0</v>
+      </c>
+      <c r="I153">
+        <v>20</v>
+      </c>
+      <c r="J153">
+        <v>0</v>
+      </c>
+      <c r="K153">
+        <v>0</v>
+      </c>
+      <c r="L153">
+        <v>6</v>
+      </c>
+      <c r="M153">
+        <v>-20</v>
+      </c>
+      <c r="N153">
+        <v>0</v>
+      </c>
+      <c r="O153">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154">
+        <v>154</v>
+      </c>
+      <c r="B154" t="str">
+        <v>["Product-248","East",396,564,732,900]</v>
+      </c>
+      <c r="C154">
+        <v>20</v>
+      </c>
+      <c r="D154">
+        <v>0</v>
+      </c>
+      <c r="E154">
+        <v>35</v>
+      </c>
+      <c r="F154">
+        <v>5</v>
+      </c>
+      <c r="G154">
+        <v>0</v>
+      </c>
+      <c r="H154">
+        <v>0</v>
+      </c>
+      <c r="I154">
+        <v>20</v>
+      </c>
+      <c r="J154">
+        <v>0</v>
+      </c>
+      <c r="K154">
+        <v>0</v>
+      </c>
+      <c r="L154">
+        <v>6</v>
+      </c>
+      <c r="M154">
+        <v>-20</v>
+      </c>
+      <c r="N154">
+        <v>0</v>
+      </c>
+      <c r="O154">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155">
+        <v>155</v>
+      </c>
+      <c r="B155" t="str">
+        <v>["Product-249","West",398,567,736,905]</v>
+      </c>
+      <c r="C155">
+        <v>20</v>
+      </c>
+      <c r="D155">
+        <v>0</v>
+      </c>
+      <c r="E155">
+        <v>35</v>
+      </c>
+      <c r="F155">
+        <v>5</v>
+      </c>
+      <c r="G155">
+        <v>0</v>
+      </c>
+      <c r="H155">
+        <v>0</v>
+      </c>
+      <c r="I155">
+        <v>20</v>
+      </c>
+      <c r="J155">
+        <v>0</v>
+      </c>
+      <c r="K155">
+        <v>0</v>
+      </c>
+      <c r="L155">
+        <v>6</v>
+      </c>
+      <c r="M155">
+        <v>-20</v>
+      </c>
+      <c r="N155">
+        <v>0</v>
+      </c>
+      <c r="O155">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156">
+        <v>156</v>
+      </c>
+      <c r="B156" t="str">
+        <v>["Product-250","East",400,570,740,910]</v>
+      </c>
+      <c r="C156">
+        <v>20</v>
+      </c>
+      <c r="D156">
+        <v>0</v>
+      </c>
+      <c r="E156">
+        <v>35</v>
+      </c>
+      <c r="F156">
+        <v>5</v>
+      </c>
+      <c r="G156">
+        <v>0</v>
+      </c>
+      <c r="H156">
+        <v>0</v>
+      </c>
+      <c r="I156">
+        <v>20</v>
+      </c>
+      <c r="J156">
+        <v>0</v>
+      </c>
+      <c r="K156">
+        <v>0</v>
+      </c>
+      <c r="L156">
+        <v>6</v>
+      </c>
+      <c r="M156">
+        <v>-20</v>
+      </c>
+      <c r="N156">
+        <v>0</v>
+      </c>
+      <c r="O156">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157">
+        <v>157</v>
+      </c>
+      <c r="B157" t="str">
+        <v>["Product-251","West",402,573,744,915]</v>
+      </c>
+      <c r="C157">
+        <v>20</v>
+      </c>
+      <c r="D157">
+        <v>0</v>
+      </c>
+      <c r="E157">
+        <v>35</v>
+      </c>
+      <c r="F157">
+        <v>5</v>
+      </c>
+      <c r="G157">
+        <v>0</v>
+      </c>
+      <c r="H157">
+        <v>0</v>
+      </c>
+      <c r="I157">
+        <v>20</v>
+      </c>
+      <c r="J157">
+        <v>0</v>
+      </c>
+      <c r="K157">
+        <v>0</v>
+      </c>
+      <c r="L157">
+        <v>6</v>
+      </c>
+      <c r="M157">
+        <v>-20</v>
+      </c>
+      <c r="N157">
+        <v>0</v>
+      </c>
+      <c r="O157">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158">
+        <v>158</v>
+      </c>
+      <c r="B158" t="str">
+        <v>["Product-252","East",404,576,748,920]</v>
+      </c>
+      <c r="C158">
+        <v>20</v>
+      </c>
+      <c r="D158">
+        <v>0</v>
+      </c>
+      <c r="E158">
+        <v>35</v>
+      </c>
+      <c r="F158">
+        <v>5</v>
+      </c>
+      <c r="G158">
+        <v>0</v>
+      </c>
+      <c r="H158">
+        <v>0</v>
+      </c>
+      <c r="I158">
+        <v>20</v>
+      </c>
+      <c r="J158">
+        <v>0</v>
+      </c>
+      <c r="K158">
+        <v>0</v>
+      </c>
+      <c r="L158">
+        <v>6</v>
+      </c>
+      <c r="M158">
+        <v>-20</v>
+      </c>
+      <c r="N158">
+        <v>0</v>
+      </c>
+      <c r="O158">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159">
+        <v>159</v>
+      </c>
+      <c r="B159" t="str">
+        <v>["Product-253","West",406,579,752,925]</v>
+      </c>
+      <c r="C159">
+        <v>20</v>
+      </c>
+      <c r="D159">
+        <v>0</v>
+      </c>
+      <c r="E159">
+        <v>35</v>
+      </c>
+      <c r="F159">
+        <v>5</v>
+      </c>
+      <c r="G159">
+        <v>0</v>
+      </c>
+      <c r="H159">
+        <v>0</v>
+      </c>
+      <c r="I159">
+        <v>20</v>
+      </c>
+      <c r="J159">
+        <v>0</v>
+      </c>
+      <c r="K159">
+        <v>0</v>
+      </c>
+      <c r="L159">
+        <v>6</v>
+      </c>
+      <c r="M159">
+        <v>-20</v>
+      </c>
+      <c r="N159">
+        <v>0</v>
+      </c>
+      <c r="O159">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160">
+        <v>160</v>
+      </c>
+      <c r="B160" t="str">
+        <v>["Product-254","East",408,582,756,930]</v>
+      </c>
+      <c r="C160">
+        <v>20</v>
+      </c>
+      <c r="D160">
+        <v>0</v>
+      </c>
+      <c r="E160">
+        <v>35</v>
+      </c>
+      <c r="F160">
+        <v>5</v>
+      </c>
+      <c r="G160">
+        <v>0</v>
+      </c>
+      <c r="H160">
+        <v>0</v>
+      </c>
+      <c r="I160">
+        <v>20</v>
+      </c>
+      <c r="J160">
+        <v>0</v>
+      </c>
+      <c r="K160">
+        <v>0</v>
+      </c>
+      <c r="L160">
+        <v>6</v>
+      </c>
+      <c r="M160">
+        <v>-20</v>
+      </c>
+      <c r="N160">
+        <v>0</v>
+      </c>
+      <c r="O160">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161">
+        <v>161</v>
+      </c>
+      <c r="B161" t="str">
+        <v>["Product-255","West",410,585,760,935]</v>
+      </c>
+      <c r="C161">
+        <v>20</v>
+      </c>
+      <c r="D161">
+        <v>0</v>
+      </c>
+      <c r="E161">
+        <v>35</v>
+      </c>
+      <c r="F161">
+        <v>5</v>
+      </c>
+      <c r="G161">
+        <v>0</v>
+      </c>
+      <c r="H161">
+        <v>0</v>
+      </c>
+      <c r="I161">
+        <v>20</v>
+      </c>
+      <c r="J161">
+        <v>0</v>
+      </c>
+      <c r="K161">
+        <v>0</v>
+      </c>
+      <c r="L161">
+        <v>6</v>
+      </c>
+      <c r="M161">
+        <v>-20</v>
+      </c>
+      <c r="N161">
+        <v>0</v>
+      </c>
+      <c r="O161">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162">
+        <v>162</v>
+      </c>
+      <c r="B162" t="str">
+        <v>["Product-256","East",412,588,764,940]</v>
+      </c>
+      <c r="C162">
+        <v>20</v>
+      </c>
+      <c r="D162">
+        <v>0</v>
+      </c>
+      <c r="E162">
+        <v>35</v>
+      </c>
+      <c r="F162">
+        <v>5</v>
+      </c>
+      <c r="G162">
+        <v>0</v>
+      </c>
+      <c r="H162">
+        <v>0</v>
+      </c>
+      <c r="I162">
+        <v>20</v>
+      </c>
+      <c r="J162">
+        <v>0</v>
+      </c>
+      <c r="K162">
+        <v>0</v>
+      </c>
+      <c r="L162">
+        <v>6</v>
+      </c>
+      <c r="M162">
+        <v>-20</v>
+      </c>
+      <c r="N162">
+        <v>0</v>
+      </c>
+      <c r="O162">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163">
+        <v>163</v>
+      </c>
+      <c r="B163" t="str">
+        <v>["Product-257","West",414,591,768,945]</v>
+      </c>
+      <c r="C163">
+        <v>20</v>
+      </c>
+      <c r="D163">
+        <v>0</v>
+      </c>
+      <c r="E163">
+        <v>35</v>
+      </c>
+      <c r="F163">
+        <v>5</v>
+      </c>
+      <c r="G163">
+        <v>0</v>
+      </c>
+      <c r="H163">
+        <v>0</v>
+      </c>
+      <c r="I163">
+        <v>20</v>
+      </c>
+      <c r="J163">
+        <v>0</v>
+      </c>
+      <c r="K163">
+        <v>0</v>
+      </c>
+      <c r="L163">
+        <v>6</v>
+      </c>
+      <c r="M163">
+        <v>-20</v>
+      </c>
+      <c r="N163">
+        <v>0</v>
+      </c>
+      <c r="O163">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164">
+        <v>164</v>
+      </c>
+      <c r="B164" t="str">
+        <v>["Product-258","East",416,594,772,950]</v>
+      </c>
+      <c r="C164">
+        <v>20</v>
+      </c>
+      <c r="D164">
+        <v>0</v>
+      </c>
+      <c r="E164">
+        <v>35</v>
+      </c>
+      <c r="F164">
+        <v>5</v>
+      </c>
+      <c r="G164">
+        <v>0</v>
+      </c>
+      <c r="H164">
+        <v>0</v>
+      </c>
+      <c r="I164">
+        <v>20</v>
+      </c>
+      <c r="J164">
+        <v>0</v>
+      </c>
+      <c r="K164">
+        <v>0</v>
+      </c>
+      <c r="L164">
+        <v>6</v>
+      </c>
+      <c r="M164">
+        <v>-20</v>
+      </c>
+      <c r="N164">
+        <v>0</v>
+      </c>
+      <c r="O164">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165">
+        <v>165</v>
+      </c>
+      <c r="B165" t="str">
+        <v>["Product-259","West",418,597,776,955]</v>
+      </c>
+      <c r="C165">
+        <v>20</v>
+      </c>
+      <c r="D165">
+        <v>0</v>
+      </c>
+      <c r="E165">
+        <v>35</v>
+      </c>
+      <c r="F165">
+        <v>5</v>
+      </c>
+      <c r="G165">
+        <v>0</v>
+      </c>
+      <c r="H165">
+        <v>0</v>
+      </c>
+      <c r="I165">
+        <v>20</v>
+      </c>
+      <c r="J165">
+        <v>0</v>
+      </c>
+      <c r="K165">
+        <v>0</v>
+      </c>
+      <c r="L165">
+        <v>6</v>
+      </c>
+      <c r="M165">
+        <v>-20</v>
+      </c>
+      <c r="N165">
+        <v>0</v>
+      </c>
+      <c r="O165">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166">
+        <v>166</v>
+      </c>
+      <c r="B166" t="str">
+        <v>["Product-260","East",420,600,780,960]</v>
+      </c>
+      <c r="C166">
+        <v>20</v>
+      </c>
+      <c r="D166">
+        <v>0</v>
+      </c>
+      <c r="E166">
+        <v>35</v>
+      </c>
+      <c r="F166">
+        <v>5</v>
+      </c>
+      <c r="G166">
+        <v>0</v>
+      </c>
+      <c r="H166">
+        <v>0</v>
+      </c>
+      <c r="I166">
+        <v>20</v>
+      </c>
+      <c r="J166">
+        <v>0</v>
+      </c>
+      <c r="K166">
+        <v>0</v>
+      </c>
+      <c r="L166">
+        <v>6</v>
+      </c>
+      <c r="M166">
+        <v>-20</v>
+      </c>
+      <c r="N166">
+        <v>0</v>
+      </c>
+      <c r="O166">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167">
+        <v>167</v>
+      </c>
+      <c r="B167" t="str">
+        <v>["Product-261","West",422,603,784,965]</v>
+      </c>
+      <c r="C167">
+        <v>20</v>
+      </c>
+      <c r="D167">
+        <v>0</v>
+      </c>
+      <c r="E167">
+        <v>35</v>
+      </c>
+      <c r="F167">
+        <v>5</v>
+      </c>
+      <c r="G167">
+        <v>0</v>
+      </c>
+      <c r="H167">
+        <v>0</v>
+      </c>
+      <c r="I167">
+        <v>20</v>
+      </c>
+      <c r="J167">
+        <v>0</v>
+      </c>
+      <c r="K167">
+        <v>0</v>
+      </c>
+      <c r="L167">
+        <v>6</v>
+      </c>
+      <c r="M167">
+        <v>-20</v>
+      </c>
+      <c r="N167">
+        <v>0</v>
+      </c>
+      <c r="O167">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168">
+        <v>168</v>
+      </c>
+      <c r="B168" t="str">
+        <v>["Product-262","East",424,606,788,970]</v>
+      </c>
+      <c r="C168">
+        <v>20</v>
+      </c>
+      <c r="D168">
+        <v>0</v>
+      </c>
+      <c r="E168">
+        <v>35</v>
+      </c>
+      <c r="F168">
+        <v>5</v>
+      </c>
+      <c r="G168">
+        <v>0</v>
+      </c>
+      <c r="H168">
+        <v>0</v>
+      </c>
+      <c r="I168">
+        <v>20</v>
+      </c>
+      <c r="J168">
+        <v>0</v>
+      </c>
+      <c r="K168">
+        <v>0</v>
+      </c>
+      <c r="L168">
+        <v>6</v>
+      </c>
+      <c r="M168">
+        <v>-20</v>
+      </c>
+      <c r="N168">
+        <v>0</v>
+      </c>
+      <c r="O168">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169">
+        <v>169</v>
+      </c>
+      <c r="B169" t="str">
+        <v>["Product-263","West",426,609,792,975]</v>
+      </c>
+      <c r="C169">
+        <v>20</v>
+      </c>
+      <c r="D169">
+        <v>0</v>
+      </c>
+      <c r="E169">
+        <v>35</v>
+      </c>
+      <c r="F169">
+        <v>5</v>
+      </c>
+      <c r="G169">
+        <v>0</v>
+      </c>
+      <c r="H169">
+        <v>0</v>
+      </c>
+      <c r="I169">
+        <v>20</v>
+      </c>
+      <c r="J169">
+        <v>0</v>
+      </c>
+      <c r="K169">
+        <v>0</v>
+      </c>
+      <c r="L169">
+        <v>6</v>
+      </c>
+      <c r="M169">
+        <v>-20</v>
+      </c>
+      <c r="N169">
+        <v>0</v>
+      </c>
+      <c r="O169">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170">
+        <v>170</v>
+      </c>
+      <c r="B170" t="str">
+        <v>["Product-264","East",428,612,796,980]</v>
+      </c>
+      <c r="C170">
+        <v>20</v>
+      </c>
+      <c r="D170">
+        <v>0</v>
+      </c>
+      <c r="E170">
+        <v>35</v>
+      </c>
+      <c r="F170">
+        <v>5</v>
+      </c>
+      <c r="G170">
+        <v>0</v>
+      </c>
+      <c r="H170">
+        <v>0</v>
+      </c>
+      <c r="I170">
+        <v>20</v>
+      </c>
+      <c r="J170">
+        <v>0</v>
+      </c>
+      <c r="K170">
+        <v>0</v>
+      </c>
+      <c r="L170">
+        <v>6</v>
+      </c>
+      <c r="M170">
+        <v>-20</v>
+      </c>
+      <c r="N170">
+        <v>0</v>
+      </c>
+      <c r="O170">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171">
+        <v>171</v>
+      </c>
+      <c r="B171" t="str">
+        <v>["Product-265","West",430,615,800,985]</v>
+      </c>
+      <c r="C171">
+        <v>20</v>
+      </c>
+      <c r="D171">
+        <v>0</v>
+      </c>
+      <c r="E171">
+        <v>35</v>
+      </c>
+      <c r="F171">
+        <v>5</v>
+      </c>
+      <c r="G171">
+        <v>0</v>
+      </c>
+      <c r="H171">
+        <v>0</v>
+      </c>
+      <c r="I171">
+        <v>20</v>
+      </c>
+      <c r="J171">
+        <v>0</v>
+      </c>
+      <c r="K171">
+        <v>0</v>
+      </c>
+      <c r="L171">
+        <v>6</v>
+      </c>
+      <c r="M171">
+        <v>-20</v>
+      </c>
+      <c r="N171">
+        <v>0</v>
+      </c>
+      <c r="O171">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172">
+        <v>172</v>
+      </c>
+      <c r="B172" t="str">
+        <v>["Product-266","East",432,618,804,990]</v>
+      </c>
+      <c r="C172">
+        <v>20</v>
+      </c>
+      <c r="D172">
+        <v>0</v>
+      </c>
+      <c r="E172">
+        <v>35</v>
+      </c>
+      <c r="F172">
+        <v>5</v>
+      </c>
+      <c r="G172">
+        <v>0</v>
+      </c>
+      <c r="H172">
+        <v>0</v>
+      </c>
+      <c r="I172">
+        <v>20</v>
+      </c>
+      <c r="J172">
+        <v>0</v>
+      </c>
+      <c r="K172">
+        <v>0</v>
+      </c>
+      <c r="L172">
+        <v>6</v>
+      </c>
+      <c r="M172">
+        <v>-20</v>
+      </c>
+      <c r="N172">
+        <v>0</v>
+      </c>
+      <c r="O172">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173">
+        <v>173</v>
+      </c>
+      <c r="B173" t="str">
+        <v>["Product-267","West",434,621,808,995]</v>
+      </c>
+      <c r="C173">
+        <v>20</v>
+      </c>
+      <c r="D173">
+        <v>0</v>
+      </c>
+      <c r="E173">
+        <v>35</v>
+      </c>
+      <c r="F173">
+        <v>5</v>
+      </c>
+      <c r="G173">
+        <v>0</v>
+      </c>
+      <c r="H173">
+        <v>0</v>
+      </c>
+      <c r="I173">
+        <v>20</v>
+      </c>
+      <c r="J173">
+        <v>0</v>
+      </c>
+      <c r="K173">
+        <v>0</v>
+      </c>
+      <c r="L173">
+        <v>6</v>
+      </c>
+      <c r="M173">
+        <v>-20</v>
+      </c>
+      <c r="N173">
+        <v>0</v>
+      </c>
+      <c r="O173">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174">
+        <v>174</v>
+      </c>
+      <c r="B174" t="str">
+        <v>["Product-268","East",436,624,812,1000]</v>
+      </c>
+      <c r="C174">
+        <v>20</v>
+      </c>
+      <c r="D174">
+        <v>0</v>
+      </c>
+      <c r="E174">
+        <v>35</v>
+      </c>
+      <c r="F174">
+        <v>5</v>
+      </c>
+      <c r="G174">
+        <v>0</v>
+      </c>
+      <c r="H174">
+        <v>0</v>
+      </c>
+      <c r="I174">
+        <v>20</v>
+      </c>
+      <c r="J174">
+        <v>0</v>
+      </c>
+      <c r="K174">
+        <v>0</v>
+      </c>
+      <c r="L174">
+        <v>6</v>
+      </c>
+      <c r="M174">
+        <v>-20</v>
+      </c>
+      <c r="N174">
+        <v>0</v>
+      </c>
+      <c r="O174">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175">
+        <v>175</v>
+      </c>
+      <c r="B175" t="str">
+        <v>["Product-269","West",438,627,816,1005]</v>
+      </c>
+      <c r="C175">
+        <v>20</v>
+      </c>
+      <c r="D175">
+        <v>0</v>
+      </c>
+      <c r="E175">
+        <v>35</v>
+      </c>
+      <c r="F175">
+        <v>5</v>
+      </c>
+      <c r="G175">
+        <v>0</v>
+      </c>
+      <c r="H175">
+        <v>0</v>
+      </c>
+      <c r="I175">
+        <v>20</v>
+      </c>
+      <c r="J175">
+        <v>0</v>
+      </c>
+      <c r="K175">
+        <v>0</v>
+      </c>
+      <c r="L175">
+        <v>6</v>
+      </c>
+      <c r="M175">
+        <v>-20</v>
+      </c>
+      <c r="N175">
+        <v>0</v>
+      </c>
+      <c r="O175">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176">
+        <v>176</v>
+      </c>
+      <c r="B176" t="str">
+        <v>["Product-270","East",440,630,820,1010]</v>
+      </c>
+      <c r="C176">
+        <v>20</v>
+      </c>
+      <c r="D176">
+        <v>0</v>
+      </c>
+      <c r="E176">
+        <v>35</v>
+      </c>
+      <c r="F176">
+        <v>5</v>
+      </c>
+      <c r="G176">
+        <v>0</v>
+      </c>
+      <c r="H176">
+        <v>0</v>
+      </c>
+      <c r="I176">
+        <v>20</v>
+      </c>
+      <c r="J176">
+        <v>0</v>
+      </c>
+      <c r="K176">
+        <v>0</v>
+      </c>
+      <c r="L176">
+        <v>6</v>
+      </c>
+      <c r="M176">
+        <v>-20</v>
+      </c>
+      <c r="N176">
+        <v>0</v>
+      </c>
+      <c r="O176">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177">
+        <v>177</v>
+      </c>
+      <c r="B177" t="str">
+        <v>["Product-271","West",442,633,824,1015]</v>
+      </c>
+      <c r="C177">
+        <v>20</v>
+      </c>
+      <c r="D177">
+        <v>0</v>
+      </c>
+      <c r="E177">
+        <v>35</v>
+      </c>
+      <c r="F177">
+        <v>5</v>
+      </c>
+      <c r="G177">
+        <v>0</v>
+      </c>
+      <c r="H177">
+        <v>0</v>
+      </c>
+      <c r="I177">
+        <v>20</v>
+      </c>
+      <c r="J177">
+        <v>0</v>
+      </c>
+      <c r="K177">
+        <v>0</v>
+      </c>
+      <c r="L177">
+        <v>6</v>
+      </c>
+      <c r="M177">
+        <v>-20</v>
+      </c>
+      <c r="N177">
+        <v>0</v>
+      </c>
+      <c r="O177">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178">
+        <v>178</v>
+      </c>
+      <c r="B178" t="str">
+        <v>["Product-272","East",444,636,828,1020]</v>
+      </c>
+      <c r="C178">
+        <v>20</v>
+      </c>
+      <c r="D178">
+        <v>0</v>
+      </c>
+      <c r="E178">
+        <v>35</v>
+      </c>
+      <c r="F178">
+        <v>5</v>
+      </c>
+      <c r="G178">
+        <v>0</v>
+      </c>
+      <c r="H178">
+        <v>0</v>
+      </c>
+      <c r="I178">
+        <v>20</v>
+      </c>
+      <c r="J178">
+        <v>0</v>
+      </c>
+      <c r="K178">
+        <v>0</v>
+      </c>
+      <c r="L178">
+        <v>6</v>
+      </c>
+      <c r="M178">
+        <v>-20</v>
+      </c>
+      <c r="N178">
+        <v>0</v>
+      </c>
+      <c r="O178">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179">
+        <v>179</v>
+      </c>
+      <c r="B179" t="str">
+        <v>["Product-273","West",446,639,832,1025]</v>
+      </c>
+      <c r="C179">
+        <v>20</v>
+      </c>
+      <c r="D179">
+        <v>0</v>
+      </c>
+      <c r="E179">
+        <v>35</v>
+      </c>
+      <c r="F179">
+        <v>5</v>
+      </c>
+      <c r="G179">
+        <v>0</v>
+      </c>
+      <c r="H179">
+        <v>0</v>
+      </c>
+      <c r="I179">
+        <v>20</v>
+      </c>
+      <c r="J179">
+        <v>0</v>
+      </c>
+      <c r="K179">
+        <v>0</v>
+      </c>
+      <c r="L179">
+        <v>6</v>
+      </c>
+      <c r="M179">
+        <v>-20</v>
+      </c>
+      <c r="N179">
+        <v>0</v>
+      </c>
+      <c r="O179">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180">
+        <v>180</v>
+      </c>
+      <c r="B180" t="str">
+        <v>["Product-274","East",448,642,836,1030]</v>
+      </c>
+      <c r="C180">
+        <v>20</v>
+      </c>
+      <c r="D180">
+        <v>0</v>
+      </c>
+      <c r="E180">
+        <v>35</v>
+      </c>
+      <c r="F180">
+        <v>5</v>
+      </c>
+      <c r="G180">
+        <v>0</v>
+      </c>
+      <c r="H180">
+        <v>0</v>
+      </c>
+      <c r="I180">
+        <v>20</v>
+      </c>
+      <c r="J180">
+        <v>0</v>
+      </c>
+      <c r="K180">
+        <v>0</v>
+      </c>
+      <c r="L180">
+        <v>6</v>
+      </c>
+      <c r="M180">
+        <v>-20</v>
+      </c>
+      <c r="N180">
+        <v>0</v>
+      </c>
+      <c r="O180">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181">
+        <v>181</v>
+      </c>
+      <c r="B181" t="str">
+        <v>["Product-275","West",450,645,840,1035]</v>
+      </c>
+      <c r="C181">
+        <v>20</v>
+      </c>
+      <c r="D181">
+        <v>0</v>
+      </c>
+      <c r="E181">
+        <v>35</v>
+      </c>
+      <c r="F181">
+        <v>5</v>
+      </c>
+      <c r="G181">
+        <v>0</v>
+      </c>
+      <c r="H181">
+        <v>0</v>
+      </c>
+      <c r="I181">
+        <v>20</v>
+      </c>
+      <c r="J181">
+        <v>0</v>
+      </c>
+      <c r="K181">
+        <v>0</v>
+      </c>
+      <c r="L181">
+        <v>6</v>
+      </c>
+      <c r="M181">
+        <v>-20</v>
+      </c>
+      <c r="N181">
+        <v>0</v>
+      </c>
+      <c r="O181">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182">
+        <v>182</v>
+      </c>
+      <c r="B182" t="str">
+        <v>["Product-276","East",452,648,844,1040]</v>
+      </c>
+      <c r="C182">
+        <v>20</v>
+      </c>
+      <c r="D182">
+        <v>0</v>
+      </c>
+      <c r="E182">
+        <v>35</v>
+      </c>
+      <c r="F182">
+        <v>5</v>
+      </c>
+      <c r="G182">
+        <v>0</v>
+      </c>
+      <c r="H182">
+        <v>0</v>
+      </c>
+      <c r="I182">
+        <v>20</v>
+      </c>
+      <c r="J182">
+        <v>0</v>
+      </c>
+      <c r="K182">
+        <v>0</v>
+      </c>
+      <c r="L182">
+        <v>6</v>
+      </c>
+      <c r="M182">
+        <v>-20</v>
+      </c>
+      <c r="N182">
+        <v>0</v>
+      </c>
+      <c r="O182">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183">
+        <v>183</v>
+      </c>
+      <c r="B183" t="str">
+        <v>["Product-277","West",454,651,848,1045]</v>
+      </c>
+      <c r="C183">
+        <v>20</v>
+      </c>
+      <c r="D183">
+        <v>0</v>
+      </c>
+      <c r="E183">
+        <v>35</v>
+      </c>
+      <c r="F183">
+        <v>5</v>
+      </c>
+      <c r="G183">
+        <v>0</v>
+      </c>
+      <c r="H183">
+        <v>0</v>
+      </c>
+      <c r="I183">
+        <v>20</v>
+      </c>
+      <c r="J183">
+        <v>0</v>
+      </c>
+      <c r="K183">
+        <v>0</v>
+      </c>
+      <c r="L183">
+        <v>6</v>
+      </c>
+      <c r="M183">
+        <v>-20</v>
+      </c>
+      <c r="N183">
+        <v>0</v>
+      </c>
+      <c r="O183">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184">
+        <v>184</v>
+      </c>
+      <c r="B184" t="str">
+        <v>["Product-278","East",456,654,852,1050]</v>
+      </c>
+      <c r="C184">
+        <v>20</v>
+      </c>
+      <c r="D184">
+        <v>0</v>
+      </c>
+      <c r="E184">
+        <v>35</v>
+      </c>
+      <c r="F184">
+        <v>5</v>
+      </c>
+      <c r="G184">
+        <v>0</v>
+      </c>
+      <c r="H184">
+        <v>0</v>
+      </c>
+      <c r="I184">
+        <v>20</v>
+      </c>
+      <c r="J184">
+        <v>0</v>
+      </c>
+      <c r="K184">
+        <v>0</v>
+      </c>
+      <c r="L184">
+        <v>6</v>
+      </c>
+      <c r="M184">
+        <v>-20</v>
+      </c>
+      <c r="N184">
+        <v>0</v>
+      </c>
+      <c r="O184">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185">
+        <v>185</v>
+      </c>
+      <c r="B185" t="str">
+        <v>["Product-279","West",458,657,856,1055]</v>
+      </c>
+      <c r="C185">
+        <v>20</v>
+      </c>
+      <c r="D185">
+        <v>0</v>
+      </c>
+      <c r="E185">
+        <v>35</v>
+      </c>
+      <c r="F185">
+        <v>5</v>
+      </c>
+      <c r="G185">
+        <v>0</v>
+      </c>
+      <c r="H185">
+        <v>0</v>
+      </c>
+      <c r="I185">
+        <v>20</v>
+      </c>
+      <c r="J185">
+        <v>0</v>
+      </c>
+      <c r="K185">
+        <v>0</v>
+      </c>
+      <c r="L185">
+        <v>6</v>
+      </c>
+      <c r="M185">
+        <v>-20</v>
+      </c>
+      <c r="N185">
+        <v>0</v>
+      </c>
+      <c r="O185">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186">
+        <v>186</v>
+      </c>
+      <c r="B186" t="str">
+        <v>["Product-280","East",460,660,860,1060]</v>
+      </c>
+      <c r="C186">
+        <v>20</v>
+      </c>
+      <c r="D186">
+        <v>0</v>
+      </c>
+      <c r="E186">
+        <v>35</v>
+      </c>
+      <c r="F186">
+        <v>5</v>
+      </c>
+      <c r="G186">
+        <v>0</v>
+      </c>
+      <c r="H186">
+        <v>0</v>
+      </c>
+      <c r="I186">
+        <v>20</v>
+      </c>
+      <c r="J186">
+        <v>0</v>
+      </c>
+      <c r="K186">
+        <v>0</v>
+      </c>
+      <c r="L186">
+        <v>6</v>
+      </c>
+      <c r="M186">
+        <v>-20</v>
+      </c>
+      <c r="N186">
+        <v>0</v>
+      </c>
+      <c r="O186">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187">
+        <v>187</v>
+      </c>
+      <c r="B187" t="str">
+        <v>["Product-281","West",462,663,864,1065]</v>
+      </c>
+      <c r="C187">
+        <v>20</v>
+      </c>
+      <c r="D187">
+        <v>0</v>
+      </c>
+      <c r="E187">
+        <v>35</v>
+      </c>
+      <c r="F187">
+        <v>5</v>
+      </c>
+      <c r="G187">
+        <v>0</v>
+      </c>
+      <c r="H187">
+        <v>0</v>
+      </c>
+      <c r="I187">
+        <v>20</v>
+      </c>
+      <c r="J187">
+        <v>0</v>
+      </c>
+      <c r="K187">
+        <v>0</v>
+      </c>
+      <c r="L187">
+        <v>6</v>
+      </c>
+      <c r="M187">
+        <v>-20</v>
+      </c>
+      <c r="N187">
+        <v>0</v>
+      </c>
+      <c r="O187">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188">
+        <v>188</v>
+      </c>
+      <c r="B188" t="str">
+        <v>["Product-282","East",464,666,868,1070]</v>
+      </c>
+      <c r="C188">
+        <v>20</v>
+      </c>
+      <c r="D188">
+        <v>0</v>
+      </c>
+      <c r="E188">
+        <v>35</v>
+      </c>
+      <c r="F188">
+        <v>5</v>
+      </c>
+      <c r="G188">
+        <v>0</v>
+      </c>
+      <c r="H188">
+        <v>0</v>
+      </c>
+      <c r="I188">
+        <v>20</v>
+      </c>
+      <c r="J188">
+        <v>0</v>
+      </c>
+      <c r="K188">
+        <v>0</v>
+      </c>
+      <c r="L188">
+        <v>6</v>
+      </c>
+      <c r="M188">
+        <v>-20</v>
+      </c>
+      <c r="N188">
+        <v>0</v>
+      </c>
+      <c r="O188">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189">
+        <v>189</v>
+      </c>
+      <c r="B189" t="str">
+        <v>["Product-283","West",466,669,872,1075]</v>
+      </c>
+      <c r="C189">
+        <v>20</v>
+      </c>
+      <c r="D189">
+        <v>0</v>
+      </c>
+      <c r="E189">
+        <v>35</v>
+      </c>
+      <c r="F189">
+        <v>5</v>
+      </c>
+      <c r="G189">
+        <v>0</v>
+      </c>
+      <c r="H189">
+        <v>0</v>
+      </c>
+      <c r="I189">
+        <v>20</v>
+      </c>
+      <c r="J189">
+        <v>0</v>
+      </c>
+      <c r="K189">
+        <v>0</v>
+      </c>
+      <c r="L189">
+        <v>6</v>
+      </c>
+      <c r="M189">
+        <v>-20</v>
+      </c>
+      <c r="N189">
+        <v>0</v>
+      </c>
+      <c r="O189">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190">
+        <v>190</v>
+      </c>
+      <c r="B190" t="str">
+        <v>["Product-284","East",468,672,876,1080]</v>
+      </c>
+      <c r="C190">
+        <v>20</v>
+      </c>
+      <c r="D190">
+        <v>0</v>
+      </c>
+      <c r="E190">
+        <v>35</v>
+      </c>
+      <c r="F190">
+        <v>5</v>
+      </c>
+      <c r="G190">
+        <v>0</v>
+      </c>
+      <c r="H190">
+        <v>0</v>
+      </c>
+      <c r="I190">
+        <v>20</v>
+      </c>
+      <c r="J190">
+        <v>0</v>
+      </c>
+      <c r="K190">
+        <v>0</v>
+      </c>
+      <c r="L190">
+        <v>6</v>
+      </c>
+      <c r="M190">
+        <v>-20</v>
+      </c>
+      <c r="N190">
+        <v>0</v>
+      </c>
+      <c r="O190">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191">
+        <v>191</v>
+      </c>
+      <c r="B191" t="str">
+        <v>["Product-285","West",470,675,880,1085]</v>
+      </c>
+      <c r="C191">
+        <v>20</v>
+      </c>
+      <c r="D191">
+        <v>0</v>
+      </c>
+      <c r="E191">
+        <v>35</v>
+      </c>
+      <c r="F191">
+        <v>5</v>
+      </c>
+      <c r="G191">
+        <v>0</v>
+      </c>
+      <c r="H191">
+        <v>0</v>
+      </c>
+      <c r="I191">
+        <v>20</v>
+      </c>
+      <c r="J191">
+        <v>0</v>
+      </c>
+      <c r="K191">
+        <v>0</v>
+      </c>
+      <c r="L191">
+        <v>6</v>
+      </c>
+      <c r="M191">
+        <v>-20</v>
+      </c>
+      <c r="N191">
+        <v>0</v>
+      </c>
+      <c r="O191">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192">
+        <v>192</v>
+      </c>
+      <c r="B192" t="str">
+        <v>["Product-286","East",472,678,884,1090]</v>
+      </c>
+      <c r="C192">
+        <v>20</v>
+      </c>
+      <c r="D192">
+        <v>0</v>
+      </c>
+      <c r="E192">
+        <v>35</v>
+      </c>
+      <c r="F192">
+        <v>5</v>
+      </c>
+      <c r="G192">
+        <v>0</v>
+      </c>
+      <c r="H192">
+        <v>0</v>
+      </c>
+      <c r="I192">
+        <v>20</v>
+      </c>
+      <c r="J192">
+        <v>0</v>
+      </c>
+      <c r="K192">
+        <v>0</v>
+      </c>
+      <c r="L192">
+        <v>6</v>
+      </c>
+      <c r="M192">
+        <v>-20</v>
+      </c>
+      <c r="N192">
+        <v>0</v>
+      </c>
+      <c r="O192">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193">
+        <v>193</v>
+      </c>
+      <c r="B193" t="str">
+        <v>["Product-287","West",474,681,888,1095]</v>
+      </c>
+      <c r="C193">
+        <v>20</v>
+      </c>
+      <c r="D193">
+        <v>0</v>
+      </c>
+      <c r="E193">
+        <v>35</v>
+      </c>
+      <c r="F193">
+        <v>5</v>
+      </c>
+      <c r="G193">
+        <v>0</v>
+      </c>
+      <c r="H193">
+        <v>0</v>
+      </c>
+      <c r="I193">
+        <v>20</v>
+      </c>
+      <c r="J193">
+        <v>0</v>
+      </c>
+      <c r="K193">
+        <v>0</v>
+      </c>
+      <c r="L193">
+        <v>6</v>
+      </c>
+      <c r="M193">
+        <v>-20</v>
+      </c>
+      <c r="N193">
+        <v>0</v>
+      </c>
+      <c r="O193">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194">
+        <v>194</v>
+      </c>
+      <c r="B194" t="str">
+        <v>["Product-288","East",476,684,892,1100]</v>
+      </c>
+      <c r="C194">
+        <v>20</v>
+      </c>
+      <c r="D194">
+        <v>0</v>
+      </c>
+      <c r="E194">
+        <v>35</v>
+      </c>
+      <c r="F194">
+        <v>5</v>
+      </c>
+      <c r="G194">
+        <v>0</v>
+      </c>
+      <c r="H194">
+        <v>0</v>
+      </c>
+      <c r="I194">
+        <v>20</v>
+      </c>
+      <c r="J194">
+        <v>0</v>
+      </c>
+      <c r="K194">
+        <v>0</v>
+      </c>
+      <c r="L194">
+        <v>6</v>
+      </c>
+      <c r="M194">
+        <v>-20</v>
+      </c>
+      <c r="N194">
+        <v>0</v>
+      </c>
+      <c r="O194">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195">
+        <v>195</v>
+      </c>
+      <c r="B195" t="str">
+        <v>["Product-289","West",478,687,896,1105]</v>
+      </c>
+      <c r="C195">
+        <v>20</v>
+      </c>
+      <c r="D195">
+        <v>0</v>
+      </c>
+      <c r="E195">
+        <v>35</v>
+      </c>
+      <c r="F195">
+        <v>5</v>
+      </c>
+      <c r="G195">
+        <v>0</v>
+      </c>
+      <c r="H195">
+        <v>0</v>
+      </c>
+      <c r="I195">
+        <v>20</v>
+      </c>
+      <c r="J195">
+        <v>0</v>
+      </c>
+      <c r="K195">
+        <v>0</v>
+      </c>
+      <c r="L195">
+        <v>6</v>
+      </c>
+      <c r="M195">
+        <v>-20</v>
+      </c>
+      <c r="N195">
+        <v>0</v>
+      </c>
+      <c r="O195">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196">
+        <v>196</v>
+      </c>
+      <c r="B196" t="str">
+        <v>["Product-290","East",480,690,900,1110]</v>
+      </c>
+      <c r="C196">
+        <v>20</v>
+      </c>
+      <c r="D196">
+        <v>0</v>
+      </c>
+      <c r="E196">
+        <v>35</v>
+      </c>
+      <c r="F196">
+        <v>5</v>
+      </c>
+      <c r="G196">
+        <v>0</v>
+      </c>
+      <c r="H196">
+        <v>0</v>
+      </c>
+      <c r="I196">
+        <v>20</v>
+      </c>
+      <c r="J196">
+        <v>0</v>
+      </c>
+      <c r="K196">
+        <v>0</v>
+      </c>
+      <c r="L196">
+        <v>6</v>
+      </c>
+      <c r="M196">
+        <v>-20</v>
+      </c>
+      <c r="N196">
+        <v>0</v>
+      </c>
+      <c r="O196">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197">
+        <v>197</v>
+      </c>
+      <c r="B197" t="str">
+        <v>["Product-291","West",482,693,904,1115]</v>
+      </c>
+      <c r="C197">
+        <v>20</v>
+      </c>
+      <c r="D197">
+        <v>0</v>
+      </c>
+      <c r="E197">
+        <v>35</v>
+      </c>
+      <c r="F197">
+        <v>5</v>
+      </c>
+      <c r="G197">
+        <v>0</v>
+      </c>
+      <c r="H197">
+        <v>0</v>
+      </c>
+      <c r="I197">
+        <v>20</v>
+      </c>
+      <c r="J197">
+        <v>0</v>
+      </c>
+      <c r="K197">
+        <v>0</v>
+      </c>
+      <c r="L197">
+        <v>6</v>
+      </c>
+      <c r="M197">
+        <v>-20</v>
+      </c>
+      <c r="N197">
+        <v>0</v>
+      </c>
+      <c r="O197">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198">
+        <v>198</v>
+      </c>
+      <c r="B198" t="str">
+        <v>["Product-292","East",484,696,908,1120]</v>
+      </c>
+      <c r="C198">
+        <v>20</v>
+      </c>
+      <c r="D198">
+        <v>0</v>
+      </c>
+      <c r="E198">
+        <v>35</v>
+      </c>
+      <c r="F198">
+        <v>5</v>
+      </c>
+      <c r="G198">
+        <v>0</v>
+      </c>
+      <c r="H198">
+        <v>0</v>
+      </c>
+      <c r="I198">
+        <v>20</v>
+      </c>
+      <c r="J198">
+        <v>0</v>
+      </c>
+      <c r="K198">
+        <v>0</v>
+      </c>
+      <c r="L198">
+        <v>6</v>
+      </c>
+      <c r="M198">
+        <v>-20</v>
+      </c>
+      <c r="N198">
+        <v>0</v>
+      </c>
+      <c r="O198">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199">
+        <v>199</v>
+      </c>
+      <c r="B199" t="str">
+        <v>["Product-293","West",486,699,912,1125]</v>
+      </c>
+      <c r="C199">
+        <v>20</v>
+      </c>
+      <c r="D199">
+        <v>0</v>
+      </c>
+      <c r="E199">
+        <v>35</v>
+      </c>
+      <c r="F199">
+        <v>5</v>
+      </c>
+      <c r="G199">
+        <v>0</v>
+      </c>
+      <c r="H199">
+        <v>0</v>
+      </c>
+      <c r="I199">
+        <v>20</v>
+      </c>
+      <c r="J199">
+        <v>0</v>
+      </c>
+      <c r="K199">
+        <v>0</v>
+      </c>
+      <c r="L199">
+        <v>6</v>
+      </c>
+      <c r="M199">
+        <v>-20</v>
+      </c>
+      <c r="N199">
+        <v>0</v>
+      </c>
+      <c r="O199">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200">
+        <v>200</v>
+      </c>
+      <c r="B200" t="str">
+        <v>["Product-294","East",488,702,916,1130]</v>
+      </c>
+      <c r="C200">
+        <v>20</v>
+      </c>
+      <c r="D200">
+        <v>0</v>
+      </c>
+      <c r="E200">
+        <v>35</v>
+      </c>
+      <c r="F200">
+        <v>5</v>
+      </c>
+      <c r="G200">
+        <v>0</v>
+      </c>
+      <c r="H200">
+        <v>0</v>
+      </c>
+      <c r="I200">
+        <v>20</v>
+      </c>
+      <c r="J200">
+        <v>0</v>
+      </c>
+      <c r="K200">
+        <v>0</v>
+      </c>
+      <c r="L200">
+        <v>6</v>
+      </c>
+      <c r="M200">
+        <v>-20</v>
+      </c>
+      <c r="N200">
+        <v>0</v>
+      </c>
+      <c r="O200">
+        <v>-100</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M20"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O200"/>
   </ignoredErrors>
 </worksheet>
 </file>